--- a/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
+++ b/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ddf5fb2bc65e958/Documentos/GitHub/lc_arquitectura_de_sistemas_de_seguridad/Administracion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{702E06F4-7ABE-4278-9F4F-32BE2150E49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F70B20E0-8ED9-4973-A91C-E751630F28CA}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{545CCF96-C524-4C47-965E-B405D4770607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{945EE14A-5570-4BC8-9146-5CEF22AA44DA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="149">
   <si>
     <t>LISTA DE ASISTENCIA — ARQUITECTURA DE SISTEMAS DE SEGURIDAD  |  Ciclo 2026-A  |  CRN 236396  |  Sección 401  |  Aula 101 Edif. 4L</t>
   </si>
@@ -729,10 +729,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -845,10 +845,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1146,70 +1142,70 @@
       <c r="E3" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23" t="s">
+      <c r="G3" s="23"/>
+      <c r="H3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="22" t="s">
+      <c r="I3" s="22"/>
+      <c r="J3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23" t="s">
+      <c r="K3" s="23"/>
+      <c r="L3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="23"/>
-      <c r="N3" s="22" t="s">
+      <c r="M3" s="22"/>
+      <c r="N3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="22"/>
-      <c r="P3" s="23" t="s">
+      <c r="O3" s="23"/>
+      <c r="P3" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="22" t="s">
+      <c r="Q3" s="22"/>
+      <c r="R3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="22"/>
-      <c r="T3" s="23" t="s">
+      <c r="S3" s="23"/>
+      <c r="T3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="23"/>
-      <c r="V3" s="22" t="s">
+      <c r="U3" s="22"/>
+      <c r="V3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="22"/>
-      <c r="X3" s="23" t="s">
+      <c r="W3" s="23"/>
+      <c r="X3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="22" t="s">
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="23" t="s">
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="AC3" s="23"/>
-      <c r="AD3" s="22" t="s">
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="23" t="s">
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="AG3" s="23"/>
-      <c r="AH3" s="22" t="s">
+      <c r="AG3" s="22"/>
+      <c r="AH3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="AI3" s="22"/>
-      <c r="AJ3" s="23" t="s">
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="AK3" s="23"/>
+      <c r="AK3" s="22"/>
       <c r="AL3" s="4" t="s">
         <v>22</v>
       </c>
@@ -1497,17 +1493,21 @@
       <c r="V6" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W6" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X6" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y6" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
+      <c r="W6" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X6" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y6" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z6" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA6" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1520,7 +1520,7 @@
       <c r="AK6" s="12"/>
       <c r="AL6" s="13">
         <f t="shared" ref="AL6:AL32" si="0">COUNTIF(F6,"A")+COUNTIF(G6,"A")+COUNTIF(H6,"A")+COUNTIF(I6,"A")+COUNTIF(J6,"A")+COUNTIF(K6,"A")+COUNTIF(L6,"A")+COUNTIF(M6,"A")+COUNTIF(N6,"A")+COUNTIF(O6,"A")+COUNTIF(P6,"A")+COUNTIF(Q6,"A")+COUNTIF(R6,"A")+COUNTIF(S6,"A")+COUNTIF(T6,"A")+COUNTIF(U6,"A")+COUNTIF(V6,"A")+COUNTIF(W6,"A")+COUNTIF(X6,"A")+COUNTIF(Y6,"A")+COUNTIF(Z6,"A")+COUNTIF(AA6,"A")+COUNTIF(AB6,"A")+COUNTIF(AC6,"A")+COUNTIF(AD6,"A")+COUNTIF(AE6,"A")+COUNTIF(AF6,"A")+COUNTIF(AG6,"A")+COUNTIF(AH6,"A")+COUNTIF(AI6,"A")+COUNTIF(AJ6,"A")+COUNTIF(AK6,"A")</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM6" s="14">
         <f t="shared" ref="AM6:AM32" si="1">COUNTIF(F6,"F")+COUNTIF(G6,"F")+COUNTIF(H6,"F")+COUNTIF(I6,"F")+COUNTIF(J6,"F")+COUNTIF(K6,"F")+COUNTIF(L6,"F")+COUNTIF(M6,"F")+COUNTIF(N6,"F")+COUNTIF(O6,"F")+COUNTIF(P6,"F")+COUNTIF(Q6,"F")+COUNTIF(R6,"F")+COUNTIF(S6,"F")+COUNTIF(T6,"F")+COUNTIF(U6,"F")+COUNTIF(V6,"F")+COUNTIF(W6,"F")+COUNTIF(X6,"F")+COUNTIF(Y6,"F")+COUNTIF(Z6,"F")+COUNTIF(AA6,"F")+COUNTIF(AB6,"F")+COUNTIF(AC6,"F")+COUNTIF(AD6,"F")+COUNTIF(AE6,"F")+COUNTIF(AF6,"F")+COUNTIF(AG6,"F")+COUNTIF(AH6,"F")+COUNTIF(AI6,"F")+COUNTIF(AJ6,"F")+COUNTIF(AK6,"F")</f>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AN6" s="15">
         <f t="shared" ref="AN6:AN32" si="2">IF(AL6=0,"",AL6/32)</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="7" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1597,16 +1597,20 @@
         <v>146</v>
       </c>
       <c r="W7" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X7" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y7" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z7" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA7" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB7" s="19"/>
       <c r="AC7" s="19"/>
       <c r="AD7" s="19"/>
@@ -1619,7 +1623,7 @@
       <c r="AK7" s="19"/>
       <c r="AL7" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM7" s="14">
         <f t="shared" si="1"/>
@@ -1627,7 +1631,7 @@
       </c>
       <c r="AN7" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1695,17 +1699,21 @@
       <c r="V8" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W8" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X8" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y8" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="12"/>
+      <c r="W8" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X8" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y8" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z8" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA8" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB8" s="12"/>
       <c r="AC8" s="12"/>
       <c r="AD8" s="12"/>
@@ -1718,7 +1726,7 @@
       <c r="AK8" s="12"/>
       <c r="AL8" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM8" s="14">
         <f t="shared" si="1"/>
@@ -1726,7 +1734,7 @@
       </c>
       <c r="AN8" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="9" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1795,16 +1803,20 @@
         <v>146</v>
       </c>
       <c r="W9" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X9" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X9" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y9" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA9" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB9" s="19"/>
       <c r="AC9" s="19"/>
       <c r="AD9" s="19"/>
@@ -1817,7 +1829,7 @@
       <c r="AK9" s="19"/>
       <c r="AL9" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" s="14">
         <f t="shared" si="1"/>
@@ -1825,7 +1837,7 @@
       </c>
       <c r="AN9" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1841,7 +1853,9 @@
       <c r="D10" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="11">
+        <v>1</v>
+      </c>
       <c r="F10" s="19" t="s">
         <v>145</v>
       </c>
@@ -1893,17 +1907,21 @@
       <c r="V10" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W10" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X10" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y10" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
+      <c r="W10" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X10" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y10" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z10" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA10" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB10" s="12"/>
       <c r="AC10" s="12"/>
       <c r="AD10" s="12"/>
@@ -1916,7 +1934,7 @@
       <c r="AK10" s="12"/>
       <c r="AL10" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM10" s="14">
         <f t="shared" si="1"/>
@@ -1924,7 +1942,7 @@
       </c>
       <c r="AN10" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1993,16 +2011,20 @@
         <v>146</v>
       </c>
       <c r="W11" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X11" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X11" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y11" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z11" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA11" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB11" s="19"/>
       <c r="AC11" s="19"/>
       <c r="AD11" s="19"/>
@@ -2015,7 +2037,7 @@
       <c r="AK11" s="19"/>
       <c r="AL11" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM11" s="14">
         <f t="shared" si="1"/>
@@ -2023,7 +2045,7 @@
       </c>
       <c r="AN11" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="12" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2093,17 +2115,21 @@
       <c r="V12" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W12" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X12" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y12" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
+      <c r="W12" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z12" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA12" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB12" s="12"/>
       <c r="AC12" s="12"/>
       <c r="AD12" s="12"/>
@@ -2116,7 +2142,7 @@
       <c r="AK12" s="12"/>
       <c r="AL12" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM12" s="14">
         <f t="shared" si="1"/>
@@ -2124,7 +2150,7 @@
       </c>
       <c r="AN12" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="13" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2193,16 +2219,20 @@
         <v>146</v>
       </c>
       <c r="W13" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X13" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X13" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y13" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z13" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA13" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB13" s="19"/>
       <c r="AC13" s="19"/>
       <c r="AD13" s="19"/>
@@ -2215,7 +2245,7 @@
       <c r="AK13" s="19"/>
       <c r="AL13" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM13" s="14">
         <f t="shared" si="1"/>
@@ -2223,7 +2253,7 @@
       </c>
       <c r="AN13" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="14" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2291,17 +2321,21 @@
       <c r="V14" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W14" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X14" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y14" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
+      <c r="W14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z14" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA14" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB14" s="12"/>
       <c r="AC14" s="12"/>
       <c r="AD14" s="12"/>
@@ -2314,7 +2348,7 @@
       <c r="AK14" s="12"/>
       <c r="AL14" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM14" s="14">
         <f t="shared" si="1"/>
@@ -2322,7 +2356,7 @@
       </c>
       <c r="AN14" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="15" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2393,16 +2427,20 @@
         <v>146</v>
       </c>
       <c r="W15" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X15" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X15" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y15" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z15" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA15" s="19" t="s">
+        <v>147</v>
+      </c>
       <c r="AB15" s="19"/>
       <c r="AC15" s="19"/>
       <c r="AD15" s="19"/>
@@ -2415,15 +2453,15 @@
       <c r="AK15" s="19"/>
       <c r="AL15" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM15" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN15" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="16" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2491,17 +2529,21 @@
       <c r="V16" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W16" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X16" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y16" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z16" s="12"/>
-      <c r="AA16" s="12"/>
+      <c r="W16" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X16" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y16" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z16" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA16" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB16" s="12"/>
       <c r="AC16" s="12"/>
       <c r="AD16" s="12"/>
@@ -2514,7 +2556,7 @@
       <c r="AK16" s="12"/>
       <c r="AL16" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM16" s="14">
         <f t="shared" si="1"/>
@@ -2522,7 +2564,7 @@
       </c>
       <c r="AN16" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="17" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2591,16 +2633,20 @@
         <v>146</v>
       </c>
       <c r="W17" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="X17" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X17" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y17" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z17" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA17" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB17" s="19"/>
       <c r="AC17" s="19"/>
       <c r="AD17" s="19"/>
@@ -2617,7 +2663,7 @@
       </c>
       <c r="AM17" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN17" s="15">
         <f t="shared" si="2"/>
@@ -2689,17 +2735,21 @@
       <c r="V18" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W18" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X18" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y18" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z18" s="12"/>
-      <c r="AA18" s="12"/>
+      <c r="W18" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X18" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y18" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z18" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA18" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB18" s="12"/>
       <c r="AC18" s="12"/>
       <c r="AD18" s="12"/>
@@ -2712,7 +2762,7 @@
       <c r="AK18" s="12"/>
       <c r="AL18" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM18" s="14">
         <f t="shared" si="1"/>
@@ -2720,7 +2770,7 @@
       </c>
       <c r="AN18" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="19" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2791,16 +2841,20 @@
         <v>146</v>
       </c>
       <c r="W19" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X19" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X19" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y19" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA19" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB19" s="19"/>
       <c r="AC19" s="19"/>
       <c r="AD19" s="19"/>
@@ -2813,7 +2867,7 @@
       <c r="AK19" s="19"/>
       <c r="AL19" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM19" s="14">
         <f t="shared" si="1"/>
@@ -2821,7 +2875,7 @@
       </c>
       <c r="AN19" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="20" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2889,17 +2943,21 @@
       <c r="V20" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W20" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X20" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y20" s="12" t="s">
+      <c r="W20" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X20" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y20" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z20" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA20" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="Z20" s="12"/>
-      <c r="AA20" s="12"/>
       <c r="AB20" s="12"/>
       <c r="AC20" s="12"/>
       <c r="AD20" s="12"/>
@@ -2912,7 +2970,7 @@
       <c r="AK20" s="12"/>
       <c r="AL20" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM20" s="14">
         <f t="shared" si="1"/>
@@ -2920,7 +2978,7 @@
       </c>
       <c r="AN20" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="21" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2989,16 +3047,20 @@
         <v>146</v>
       </c>
       <c r="W21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X21" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X21" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y21" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z21" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA21" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB21" s="19"/>
       <c r="AC21" s="19"/>
       <c r="AD21" s="19"/>
@@ -3015,7 +3077,7 @@
       </c>
       <c r="AM21" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN21" s="15">
         <f t="shared" si="2"/>
@@ -3087,17 +3149,21 @@
       <c r="V22" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W22" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X22" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y22" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="12"/>
+      <c r="W22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z22" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA22" s="12" t="s">
+        <v>147</v>
+      </c>
       <c r="AB22" s="12"/>
       <c r="AC22" s="12"/>
       <c r="AD22" s="12"/>
@@ -3110,15 +3176,15 @@
       <c r="AK22" s="12"/>
       <c r="AL22" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM22" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="23" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3187,16 +3253,20 @@
         <v>146</v>
       </c>
       <c r="W23" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X23" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X23" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y23" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA23" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB23" s="19"/>
       <c r="AC23" s="19"/>
       <c r="AD23" s="19"/>
@@ -3209,7 +3279,7 @@
       <c r="AK23" s="19"/>
       <c r="AL23" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM23" s="14">
         <f t="shared" si="1"/>
@@ -3217,7 +3287,7 @@
       </c>
       <c r="AN23" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="24" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3285,17 +3355,21 @@
       <c r="V24" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W24" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X24" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y24" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z24" s="12"/>
-      <c r="AA24" s="12"/>
+      <c r="W24" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X24" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y24" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z24" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA24" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB24" s="12"/>
       <c r="AC24" s="12"/>
       <c r="AD24" s="12"/>
@@ -3308,7 +3382,7 @@
       <c r="AK24" s="12"/>
       <c r="AL24" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM24" s="14">
         <f t="shared" si="1"/>
@@ -3316,7 +3390,7 @@
       </c>
       <c r="AN24" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="25" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3385,16 +3459,20 @@
         <v>146</v>
       </c>
       <c r="W25" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X25" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X25" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y25" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z25" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA25" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB25" s="19"/>
       <c r="AC25" s="19"/>
       <c r="AD25" s="19"/>
@@ -3407,7 +3485,7 @@
       <c r="AK25" s="19"/>
       <c r="AL25" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM25" s="14">
         <f t="shared" si="1"/>
@@ -3415,7 +3493,7 @@
       </c>
       <c r="AN25" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="26" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3483,17 +3561,21 @@
       <c r="V26" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W26" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X26" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y26" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z26" s="12"/>
-      <c r="AA26" s="12"/>
+      <c r="W26" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X26" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y26" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z26" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA26" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB26" s="12"/>
       <c r="AC26" s="12"/>
       <c r="AD26" s="12"/>
@@ -3506,7 +3588,7 @@
       <c r="AK26" s="12"/>
       <c r="AL26" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM26" s="14">
         <f t="shared" si="1"/>
@@ -3514,7 +3596,7 @@
       </c>
       <c r="AN26" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="27" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3583,16 +3665,20 @@
         <v>146</v>
       </c>
       <c r="W27" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X27" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X27" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y27" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z27" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA27" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB27" s="19"/>
       <c r="AC27" s="19"/>
       <c r="AD27" s="19"/>
@@ -3605,7 +3691,7 @@
       <c r="AK27" s="19"/>
       <c r="AL27" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM27" s="14">
         <f t="shared" si="1"/>
@@ -3613,7 +3699,7 @@
       </c>
       <c r="AN27" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="28" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3681,17 +3767,21 @@
       <c r="V28" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W28" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="X28" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y28" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z28" s="12"/>
-      <c r="AA28" s="12"/>
+      <c r="W28" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X28" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y28" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z28" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA28" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB28" s="12"/>
       <c r="AC28" s="12"/>
       <c r="AD28" s="12"/>
@@ -3704,15 +3794,15 @@
       <c r="AK28" s="12"/>
       <c r="AL28" s="13">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM28" s="14">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN28" s="15">
         <f t="shared" si="2"/>
-        <v>0.53125</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="29" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3728,7 +3818,9 @@
       <c r="D29" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="18"/>
+      <c r="E29" s="18">
+        <v>1</v>
+      </c>
       <c r="F29" s="19" t="s">
         <v>145</v>
       </c>
@@ -3781,16 +3873,20 @@
         <v>146</v>
       </c>
       <c r="W29" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X29" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X29" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y29" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z29" s="19"/>
-      <c r="AA29" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z29" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA29" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB29" s="19"/>
       <c r="AC29" s="19"/>
       <c r="AD29" s="19"/>
@@ -3803,7 +3899,7 @@
       <c r="AK29" s="19"/>
       <c r="AL29" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM29" s="14">
         <f t="shared" si="1"/>
@@ -3811,7 +3907,7 @@
       </c>
       <c r="AN29" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="30" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3881,17 +3977,21 @@
       <c r="V30" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W30" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X30" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y30" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z30" s="12"/>
-      <c r="AA30" s="12"/>
+      <c r="W30" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X30" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y30" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z30" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA30" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB30" s="12"/>
       <c r="AC30" s="12"/>
       <c r="AD30" s="12"/>
@@ -3904,7 +4004,7 @@
       <c r="AK30" s="12"/>
       <c r="AL30" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM30" s="14">
         <f t="shared" si="1"/>
@@ -3912,7 +4012,7 @@
       </c>
       <c r="AN30" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3983,16 +4083,20 @@
         <v>146</v>
       </c>
       <c r="W31" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="X31" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="X31" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="Y31" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="19"/>
+        <v>146</v>
+      </c>
+      <c r="Z31" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA31" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="AB31" s="19"/>
       <c r="AC31" s="19"/>
       <c r="AD31" s="19"/>
@@ -4005,7 +4109,7 @@
       <c r="AK31" s="19"/>
       <c r="AL31" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM31" s="14">
         <f t="shared" si="1"/>
@@ -4013,7 +4117,7 @@
       </c>
       <c r="AN31" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="32" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4083,17 +4187,21 @@
       <c r="V32" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="W32" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="X32" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y32" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z32" s="12"/>
-      <c r="AA32" s="12"/>
+      <c r="W32" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="X32" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y32" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z32" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA32" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AB32" s="12"/>
       <c r="AC32" s="12"/>
       <c r="AD32" s="12"/>
@@ -4106,7 +4214,7 @@
       <c r="AK32" s="12"/>
       <c r="AL32" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM32" s="14">
         <f t="shared" si="1"/>
@@ -4114,7 +4222,7 @@
       </c>
       <c r="AN32" s="15">
         <f t="shared" si="2"/>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="33" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4195,23 +4303,23 @@
       </c>
       <c r="W33" s="20">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X33" s="20">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB33" s="20">
         <f t="shared" si="3"/>
@@ -4303,7 +4411,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AJ3:AK3"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A34:AN34"/>
     <mergeCell ref="A1:AN1"/>
@@ -4323,6 +4430,7 @@
     <mergeCell ref="AD3:AE3"/>
     <mergeCell ref="AF3:AG3"/>
     <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="AN6:AN32">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -4404,7 +4512,7 @@
       </c>
       <c r="E3" s="13">
         <f>Asistencia!AL6</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="14">
         <f>Asistencia!AM6</f>
@@ -4412,7 +4520,7 @@
       </c>
       <c r="G3" s="15">
         <f>Asistencia!AN6</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H3" s="9" t="str">
         <f>IF(Asistencia!AN6="","Sin datos",IF(Asistencia!AN6&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4434,7 +4542,7 @@
       </c>
       <c r="E4" s="13">
         <f>Asistencia!AL7</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="14">
         <f>Asistencia!AM7</f>
@@ -4442,7 +4550,7 @@
       </c>
       <c r="G4" s="15">
         <f>Asistencia!AN7</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H4" s="16" t="str">
         <f>IF(Asistencia!AN7="","Sin datos",IF(Asistencia!AN7&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4464,7 +4572,7 @@
       </c>
       <c r="E5" s="13">
         <f>Asistencia!AL8</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" s="14">
         <f>Asistencia!AM8</f>
@@ -4472,7 +4580,7 @@
       </c>
       <c r="G5" s="15">
         <f>Asistencia!AN8</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H5" s="9" t="str">
         <f>IF(Asistencia!AN8="","Sin datos",IF(Asistencia!AN8&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4494,7 +4602,7 @@
       </c>
       <c r="E6" s="13">
         <f>Asistencia!AL9</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="14">
         <f>Asistencia!AM9</f>
@@ -4502,7 +4610,7 @@
       </c>
       <c r="G6" s="15">
         <f>Asistencia!AN9</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H6" s="16" t="str">
         <f>IF(Asistencia!AN9="","Sin datos",IF(Asistencia!AN9&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4524,7 +4632,7 @@
       </c>
       <c r="E7" s="13">
         <f>Asistencia!AL10</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="14">
         <f>Asistencia!AM10</f>
@@ -4532,7 +4640,7 @@
       </c>
       <c r="G7" s="15">
         <f>Asistencia!AN10</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H7" s="9" t="str">
         <f>IF(Asistencia!AN10="","Sin datos",IF(Asistencia!AN10&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4554,7 +4662,7 @@
       </c>
       <c r="E8" s="13">
         <f>Asistencia!AL11</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" s="14">
         <f>Asistencia!AM11</f>
@@ -4562,7 +4670,7 @@
       </c>
       <c r="G8" s="15">
         <f>Asistencia!AN11</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H8" s="16" t="str">
         <f>IF(Asistencia!AN11="","Sin datos",IF(Asistencia!AN11&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4584,7 +4692,7 @@
       </c>
       <c r="E9" s="13">
         <f>Asistencia!AL12</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="14">
         <f>Asistencia!AM12</f>
@@ -4592,7 +4700,7 @@
       </c>
       <c r="G9" s="15">
         <f>Asistencia!AN12</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H9" s="9" t="str">
         <f>IF(Asistencia!AN12="","Sin datos",IF(Asistencia!AN12&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4614,7 +4722,7 @@
       </c>
       <c r="E10" s="13">
         <f>Asistencia!AL13</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="14">
         <f>Asistencia!AM13</f>
@@ -4622,7 +4730,7 @@
       </c>
       <c r="G10" s="15">
         <f>Asistencia!AN13</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H10" s="16" t="str">
         <f>IF(Asistencia!AN13="","Sin datos",IF(Asistencia!AN13&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4644,7 +4752,7 @@
       </c>
       <c r="E11" s="13">
         <f>Asistencia!AL14</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" s="14">
         <f>Asistencia!AM14</f>
@@ -4652,7 +4760,7 @@
       </c>
       <c r="G11" s="15">
         <f>Asistencia!AN14</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H11" s="9" t="str">
         <f>IF(Asistencia!AN14="","Sin datos",IF(Asistencia!AN14&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4674,15 +4782,15 @@
       </c>
       <c r="E12" s="13">
         <f>Asistencia!AL15</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F12" s="14">
         <f>Asistencia!AM15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="15">
         <f>Asistencia!AN15</f>
-        <v>0.59375</v>
+        <v>0.53125</v>
       </c>
       <c r="H12" s="16" t="str">
         <f>IF(Asistencia!AN15="","Sin datos",IF(Asistencia!AN15&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4704,7 +4812,7 @@
       </c>
       <c r="E13" s="13">
         <f>Asistencia!AL16</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="14">
         <f>Asistencia!AM16</f>
@@ -4712,7 +4820,7 @@
       </c>
       <c r="G13" s="15">
         <f>Asistencia!AN16</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H13" s="9" t="str">
         <f>IF(Asistencia!AN16="","Sin datos",IF(Asistencia!AN16&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4738,7 +4846,7 @@
       </c>
       <c r="F14" s="14">
         <f>Asistencia!AM17</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="15">
         <f>Asistencia!AN17</f>
@@ -4764,7 +4872,7 @@
       </c>
       <c r="E15" s="13">
         <f>Asistencia!AL18</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" s="14">
         <f>Asistencia!AM18</f>
@@ -4772,7 +4880,7 @@
       </c>
       <c r="G15" s="15">
         <f>Asistencia!AN18</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H15" s="9" t="str">
         <f>IF(Asistencia!AN18="","Sin datos",IF(Asistencia!AN18&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4794,7 +4902,7 @@
       </c>
       <c r="E16" s="13">
         <f>Asistencia!AL19</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" s="14">
         <f>Asistencia!AM19</f>
@@ -4802,7 +4910,7 @@
       </c>
       <c r="G16" s="15">
         <f>Asistencia!AN19</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H16" s="16" t="str">
         <f>IF(Asistencia!AN19="","Sin datos",IF(Asistencia!AN19&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4824,7 +4932,7 @@
       </c>
       <c r="E17" s="13">
         <f>Asistencia!AL20</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="14">
         <f>Asistencia!AM20</f>
@@ -4832,7 +4940,7 @@
       </c>
       <c r="G17" s="15">
         <f>Asistencia!AN20</f>
-        <v>0.5625</v>
+        <v>0.53125</v>
       </c>
       <c r="H17" s="9" t="str">
         <f>IF(Asistencia!AN20="","Sin datos",IF(Asistencia!AN20&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4858,7 +4966,7 @@
       </c>
       <c r="F18" s="14">
         <f>Asistencia!AM21</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="15">
         <f>Asistencia!AN21</f>
@@ -4884,15 +4992,15 @@
       </c>
       <c r="E19" s="13">
         <f>Asistencia!AL22</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F19" s="14">
         <f>Asistencia!AM22</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="15">
         <f>Asistencia!AN22</f>
-        <v>0.59375</v>
+        <v>0.53125</v>
       </c>
       <c r="H19" s="9" t="str">
         <f>IF(Asistencia!AN22="","Sin datos",IF(Asistencia!AN22&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4914,7 +5022,7 @@
       </c>
       <c r="E20" s="13">
         <f>Asistencia!AL23</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" s="14">
         <f>Asistencia!AM23</f>
@@ -4922,7 +5030,7 @@
       </c>
       <c r="G20" s="15">
         <f>Asistencia!AN23</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H20" s="16" t="str">
         <f>IF(Asistencia!AN23="","Sin datos",IF(Asistencia!AN23&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4944,7 +5052,7 @@
       </c>
       <c r="E21" s="13">
         <f>Asistencia!AL24</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" s="14">
         <f>Asistencia!AM24</f>
@@ -4952,7 +5060,7 @@
       </c>
       <c r="G21" s="15">
         <f>Asistencia!AN24</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H21" s="9" t="str">
         <f>IF(Asistencia!AN24="","Sin datos",IF(Asistencia!AN24&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -4974,7 +5082,7 @@
       </c>
       <c r="E22" s="13">
         <f>Asistencia!AL25</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="14">
         <f>Asistencia!AM25</f>
@@ -4982,7 +5090,7 @@
       </c>
       <c r="G22" s="15">
         <f>Asistencia!AN25</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H22" s="16" t="str">
         <f>IF(Asistencia!AN25="","Sin datos",IF(Asistencia!AN25&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5004,7 +5112,7 @@
       </c>
       <c r="E23" s="13">
         <f>Asistencia!AL26</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F23" s="14">
         <f>Asistencia!AM26</f>
@@ -5012,7 +5120,7 @@
       </c>
       <c r="G23" s="15">
         <f>Asistencia!AN26</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H23" s="9" t="str">
         <f>IF(Asistencia!AN26="","Sin datos",IF(Asistencia!AN26&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5034,7 +5142,7 @@
       </c>
       <c r="E24" s="13">
         <f>Asistencia!AL27</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" s="14">
         <f>Asistencia!AM27</f>
@@ -5042,7 +5150,7 @@
       </c>
       <c r="G24" s="15">
         <f>Asistencia!AN27</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H24" s="16" t="str">
         <f>IF(Asistencia!AN27="","Sin datos",IF(Asistencia!AN27&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5064,15 +5172,15 @@
       </c>
       <c r="E25" s="13">
         <f>Asistencia!AL28</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F25" s="14">
         <f>Asistencia!AM28</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="15">
         <f>Asistencia!AN28</f>
-        <v>0.53125</v>
+        <v>0.5625</v>
       </c>
       <c r="H25" s="9" t="str">
         <f>IF(Asistencia!AN28="","Sin datos",IF(Asistencia!AN28&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5094,7 +5202,7 @@
       </c>
       <c r="E26" s="13">
         <f>Asistencia!AL29</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" s="14">
         <f>Asistencia!AM29</f>
@@ -5102,7 +5210,7 @@
       </c>
       <c r="G26" s="15">
         <f>Asistencia!AN29</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H26" s="16" t="str">
         <f>IF(Asistencia!AN29="","Sin datos",IF(Asistencia!AN29&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5124,7 +5232,7 @@
       </c>
       <c r="E27" s="13">
         <f>Asistencia!AL30</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" s="14">
         <f>Asistencia!AM30</f>
@@ -5132,7 +5240,7 @@
       </c>
       <c r="G27" s="15">
         <f>Asistencia!AN30</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H27" s="9" t="str">
         <f>IF(Asistencia!AN30="","Sin datos",IF(Asistencia!AN30&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5154,7 +5262,7 @@
       </c>
       <c r="E28" s="13">
         <f>Asistencia!AL31</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F28" s="14">
         <f>Asistencia!AM31</f>
@@ -5162,7 +5270,7 @@
       </c>
       <c r="G28" s="15">
         <f>Asistencia!AN31</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H28" s="16" t="str">
         <f>IF(Asistencia!AN31="","Sin datos",IF(Asistencia!AN31&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5184,7 +5292,7 @@
       </c>
       <c r="E29" s="13">
         <f>Asistencia!AL32</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" s="14">
         <f>Asistencia!AM32</f>
@@ -5192,7 +5300,7 @@
       </c>
       <c r="G29" s="15">
         <f>Asistencia!AN32</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
       <c r="H29" s="9" t="str">
         <f>IF(Asistencia!AN32="","Sin datos",IF(Asistencia!AN32&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>

--- a/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
+++ b/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ddf5fb2bc65e958/Documentos/GitHub/lc_arquitectura_de_sistemas_de_seguridad/Administracion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="14_{545CCF96-C524-4C47-965E-B405D4770607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{945EE14A-5570-4BC8-9146-5CEF22AA44DA}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="14_{545CCF96-C524-4C47-965E-B405D4770607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0917CE8-AE5F-45EE-89F9-3D12D5AE14D3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asistencia" sheetId="1" r:id="rId1"/>
     <sheet name="Resumen" sheetId="2" r:id="rId2"/>
+    <sheet name="Examen 1" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Examen 1'!$A$1:$Z$27</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="305">
   <si>
     <t>LISTA DE ASISTENCIA — ARQUITECTURA DE SISTEMAS DE SEGURIDAD  |  Ciclo 2026-A  |  CRN 236396  |  Sección 401  |  Aula 101 Edif. 4L</t>
   </si>
@@ -483,7 +487,512 @@
     <t>F</t>
   </si>
   <si>
-    <t>Puntos Extra</t>
+    <t>Examen 1</t>
+  </si>
+  <si>
+    <t>Examen 2</t>
+  </si>
+  <si>
+    <t>Marca temporal</t>
+  </si>
+  <si>
+    <t>Dirección de correo electrónico</t>
+  </si>
+  <si>
+    <t>Puntuación</t>
+  </si>
+  <si>
+    <t>1. Una empresa descubre que un atacante accedió a su base de datos de clientes y copió 2 millones de registros sin modificar nada. ¿Qué pilar del CIA Triad fue violado?</t>
+  </si>
+  <si>
+    <t>2. Un hospital configura su sistema de expedientes para que los médicos solo puedan ver los expedientes de sus propios pacientes, y el personal administrativo solo vea datos de facturación. ¿Qué principio de diseño está aplicando?</t>
+  </si>
+  <si>
+    <t>3. ¿Cuál de las siguientes afirmaciones describe correctamente la diferencia entre el modelo perimetral y Zero Trust?</t>
+  </si>
+  <si>
+    <t>4. ¿Cuál de los siguientes marcos de seguridad es el único certificable por una auditoría externa?</t>
+  </si>
+  <si>
+    <t>5. Un ransomware cifra todos los archivos de una empresa y pide rescate para devolver el acceso. ¿Qué pilar o pilares del CIA Triad fueron afectados?</t>
+  </si>
+  <si>
+    <t>6. En el ataque a Uber (2022), el atacante convenció a un empleado de aprobar una solicitud de MFA falsa. Una vez dentro, encontró credenciales de administrador en un script de PowerShell en una carpeta compartida. ¿Qué principio de diseño fue violado al guardar esas credenciales en un lugar accesible para cualquier empleado?</t>
+  </si>
+  <si>
+    <t>7. CIS Controls organiza sus 18 controles en tres grupos de implementación. ¿Qué describe correctamente el Grupo IG1?</t>
+  </si>
+  <si>
+    <t>8. ¿En qué fase del ciclo de vida de la arquitectura de seguridad se realizan auditorías y pruebas de penetración?</t>
+  </si>
+  <si>
+    <t>9. NIST CSF 2.0 agregó una nueva función que no existía en la versión 1.1. ¿Cuál es y qué pregunta responde?</t>
+  </si>
+  <si>
+    <t>10. En el ataque a SolarWinds (2020), los atacantes insertaron código malicioso en actualizaciones legítimas del software Orion. ¿Qué fase del ciclo de vida de la arquitectura de seguridad falló principalmente?</t>
+  </si>
+  <si>
+    <t>11. Zero Trust es un producto de seguridad que se compra e instala como un firewall.</t>
+  </si>
+  <si>
+    <t>12. El hashing SHA-256 protege principalmente la Integridad de los datos porque genera una huella digital que detecta modificaciones.</t>
+  </si>
+  <si>
+    <t>13. NIST CSF es obligatorio para todas las empresas que operan en Estados Unidos.</t>
+  </si>
+  <si>
+    <t>14. La defensa en profundidad y la redundancia son lo mismo: ambas duplican controles para mayor seguridad.</t>
+  </si>
+  <si>
+    <t>15. Los cinco pilares de Zero Trust según NIST SP 800-207 son: Identidad, Dispositivo, Red, Aplicación y Datos.</t>
+  </si>
+  <si>
+    <t>16. En el modelo perimetral, una vez que un atacante cruza el firewall tiene acceso libre a todo el interior de la red.</t>
+  </si>
+  <si>
+    <t>17. ISO 27001 impone los mismos controles técnicos específicos a todas las organizaciones sin importar su contexto.</t>
+  </si>
+  <si>
+    <t>18. La disponibilidad se viola únicamente cuando hay un ataque intencional como un DDoS, no por fallos de hardware.</t>
+  </si>
+  <si>
+    <t>19. CIS Controls v8 tiene una prescripción alta porque te dice exactamente qué hacer, no solo qué lograr.</t>
+  </si>
+  <si>
+    <t>20. El ciclo de vida de la arquitectura de seguridad es un proceso que se ejecuta una sola vez al diseñar el sistema.</t>
+  </si>
+  <si>
+    <t>21. El siguiente escenario combina conceptos de las tres sesiones que tuvimos. 
+Léelo con cuidado y responde lo que se pide. 
+Una startup de tecnología financiera almacena datos de tarjetas de crédito de sus usuarios. Su equipo de desarrollo tiene acceso completo a la base de datos de producción para "agilizar las correcciones de bugs". No tienen ningún marco de seguridad implementado formalmente. Un día, un desarrollador con acceso a producción renuncia molesto y antes de irse descarga 50,000 registros de tarjetas. El incidente no se detecta hasta tres meses después cuando los usuarios reportan cargos no reconocidos. 
+Responde las tres preguntas siguientes en no más de 8 líneas en total:
+- ¿Qué pilar o pilares del CIA Triad fueron violados y cómo? 
+- ¿Qué principio de diseño habría limitado el daño si hubiera estado implementado desde el inicio? 
+- ¿Qué marco de seguridad le recomendarías a esta empresa como punto de partida y por qué ese específicamente?</t>
+  </si>
+  <si>
+    <t>a) Defensa en profundidad</t>
+  </si>
+  <si>
+    <t>a) El modelo perimetral verifica cada solicitud continuamente</t>
+  </si>
+  <si>
+    <t>c) ISO 27001</t>
+  </si>
+  <si>
+    <t>b) Integridad y Disponibilidad</t>
+  </si>
+  <si>
+    <t>a) Controles para infraestructura crítica que incluyen pruebas de penetración</t>
+  </si>
+  <si>
+    <t>c) RESPOND — ¿Qué hacemos cuando ocurre un incidente?</t>
+  </si>
+  <si>
+    <t>Falso</t>
+  </si>
+  <si>
+    <t>Verdadero</t>
+  </si>
+  <si>
+    <t>edgar.gonzalez1780@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>94 / 110</t>
+  </si>
+  <si>
+    <t>c) Solo Confidencialidad</t>
+  </si>
+  <si>
+    <t>d) Zero Trust</t>
+  </si>
+  <si>
+    <t>b) Zero Trust asume que nada es confiable por defecto</t>
+  </si>
+  <si>
+    <t>b) Mínimo privilegio</t>
+  </si>
+  <si>
+    <t>c) Higiene básica que toda organización debe implementar y que evita el 85% de los ataques comunes</t>
+  </si>
+  <si>
+    <t>d) Fase 4 - Verificación y validación</t>
+  </si>
+  <si>
+    <t>b) GOVERN — ¿Cómo se toman las decisiones de seguridad?</t>
+  </si>
+  <si>
+    <t>Fase 3 — Implementación sin validación de integridad y Fase 4 — Monitoreo insuficiente</t>
+  </si>
+  <si>
+    <t>Confidencialidad e integridad , detección y principio del menor privilegio , nist ya que es flexible</t>
+  </si>
+  <si>
+    <t>mahonri.martinez6831@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>110 / 110</t>
+  </si>
+  <si>
+    <t>c) Mínimo privilegio</t>
+  </si>
+  <si>
+    <t>CIA: Se violo la Confidencialidad por el robo de datos y la Integridad 
+Principio: Mínimo Privilegio para que no tuviera acceso si no era necesario
+Marco: CIS Controls (IG1), o Zero trust ya que al ser datos bancarios son muy delicados , y tienen que estar muy bien organizados y limpios .</t>
+  </si>
+  <si>
+    <t>joshua.munoz6454@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>100 / 110</t>
+  </si>
+  <si>
+    <t>1 se violo la confidencialidad y la integridad de forma indirecta al perder el control sobre informacion sensible
+2 el principio que habria limitado el daño es el pricipio de minimo privilegio 
+3 se recomienda CIS controls v8 como un punto de partida bastante bueno ya que es practico, prescriptivo y ayuda con controles basicos</t>
+  </si>
+  <si>
+    <t>paola.fregoso5920@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>88 / 110</t>
+  </si>
+  <si>
+    <t>c) Solo Disponibilidad</t>
+  </si>
+  <si>
+    <t>c) Segmentación</t>
+  </si>
+  <si>
+    <t>1. La confidencialidad ya que los empleados al ya no formar parte de la empresa, toda información perteneciente a ella ya es confidencial.
+2. Que los desarrolladores no tuvieran acceso a la información financiera
+3. El NIST ya que brinda instrucciones concretas del diseño de Arquitectura</t>
+  </si>
+  <si>
+    <t>allison.lazos8860@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>104 / 110</t>
+  </si>
+  <si>
+    <t>1. La confidencialidad ya que se descargó sin autorizacion los registros, la integridad al estar el riesgo de manipulacion de datos.
+2.Mínimo privilegio habría limitado el daño, pues los desarrolladores no deberían tener acceso directo a la base de datos de producción con información sensible.
+3.El ISO 27001, porque ofrece un sistema formal y flexible de gestión de la seguridad de la información.</t>
+  </si>
+  <si>
+    <t>daphne.franco0514@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>Se violó la confidencialidad(los 50,000 registros de tarjetas fueron sustraídos sin autorización) e integridad (por el acceso completo que permitía las modificaciones no autorizadas a los datos. 
+Considero que el principio "mínimo privilegio" habría limitado el daño al restringir acceso del desarrollador para que cada quien tenga solo lo necesario para su función. Como marco de partida recomendaría el CIS Controls v8 porque es altamente prescriptivo y prioriza acciones concretas.</t>
+  </si>
+  <si>
+    <t>andrea.carcano4900@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>Se violan los pilares de confidencialidad, ya que, si bien no modificó ni hizo que se cayera ningún servicio, robó los datos para beneficio propio, debieron tener principalmente un mínimo privilegio para que no todas las personas pudieran acceder a estos servicios solo porque sí. Además, recomendaría el NIST, ya que siento que es un marco que se puede adaptar a las empresas fácilmente.</t>
+  </si>
+  <si>
+    <t>juan.geraldo6455@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>El pilar que de la Triada de la Ciberseguridad que fue violado es el de la confidencialidad, puesto que la información sensible de los clientes debe de estar resguardado. El principio de diseño que habría limitado el daño en caso de ser implementado sería el de Privilegio Mínimo, puesto que los desarrolladores no debieron tener acceso a producción. El marco de seguridad recomendado para la startup es el CIS Controls (IG1), porque ofrece "higiene básica" para detener ataques comunes y organizar privilegios rápidamente.</t>
+  </si>
+  <si>
+    <t>christian.reyes5675@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>90 / 110</t>
+  </si>
+  <si>
+    <t>d) Los tres pilares simultáneamente</t>
+  </si>
+  <si>
+    <t>d) Disponibilidad</t>
+  </si>
+  <si>
+    <t>Se viola la confidencialidad pues accede a los datos de los registros de tarjetas de losusuarios, se hubiera evitado si se hubiera diseñado con PDCA plan do check act, se recomendaria el NIS de confidencialidad, integridad y disponibilidad, asi como el zero trust con minimos privilegios, tambien se recomienda auditorias para detectar mas rapido el evento fue anomalo la descarga de los datos pero no tenian un NGFW para detectar la anomalia por el ID- de usuario</t>
+  </si>
+  <si>
+    <t>liliana.gonzalez1038@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>98 / 110</t>
+  </si>
+  <si>
+    <t>b) Controles para organizaciones con datos sensibles que agregan gestión de vulnerabilidades</t>
+  </si>
+  <si>
+    <t>Confidencialidad e integridad porque se expusieron los datos de los clientes y con ellos la integridad de la empresa, ya no hay confianza por tardar demasiado en detectarlo.
+Principio del mínimo privilegio 
+NIST CSF para la construcción de una buena estrategia de seguridad</t>
+  </si>
+  <si>
+    <t>jorge.ponce1098@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>64 / 110</t>
+  </si>
+  <si>
+    <t>b) Segmentación</t>
+  </si>
+  <si>
+    <t>d) Los tres son certificables</t>
+  </si>
+  <si>
+    <t>R1 = Confidencialidad e integridad
+R2 = Que tuviera defensa en profundidad, ya que aun que sea el desarrollador, debería tener un limite en cuanto a los datos que ve.
+R3 = Dependería bajo que leyes de que país estén regidos, pero vamos a suponer que están en México recomendaría ISO 27001, ya que es lo mínimo que deberían de tener al no tener nada establecido</t>
+  </si>
+  <si>
+    <t>fabian.zaragoza1777@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>106 / 110</t>
+  </si>
+  <si>
+    <t>- ¿Qué pilar o pilares del CIA Triad fueron violados y cómo? R:Confidencialidad ya que el desarrollador extrajo información sensible (tarjetas de crédito) sin autorización.
+- ¿Qué principio de diseño habría limitado el daño si hubiera estado implementado desde el inicio? R: El principio de Mínimo Privilegio habría evitado esto; los desarrolladores no necesitan acceso total a la base de datos de producción para corregir bugs.
+- ¿Qué marco de seguridad le recomendarías a esta empresa como punto de partida y por qué ese específicamente? R: Recomendaría empezar con CIS Controls (Grupo IG1). Al ser una startup que empieza de cero, este marco es ideal porque les dirá exactamente qué controles técnicos de "higiene básica" implementar paso a paso.</t>
+  </si>
+  <si>
+    <t>25/03/2026 10:03:50</t>
+  </si>
+  <si>
+    <t>erick.gomez@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>54 / 110</t>
+  </si>
+  <si>
+    <t>d) Confidencialidad e Integridad</t>
+  </si>
+  <si>
+    <t>c) Fase 3 - Implementación</t>
+  </si>
+  <si>
+    <t>Fase 2 — Diseño de arquitectura</t>
+  </si>
+  <si>
+    <t>el pilar de la CIA que afecta fue la confianza ya que los empleados confiaron sus datos y fueron utilizados de forma errónea y no se dieron cuanta .
+si la infraestructura hubiera estado diseñada con confianza mínima los empleados comunes no podrían acceder a los datos y centralizar la información en un centro donde tendrían acceso es una falla critica de seguridad ya que jamas hay que confiar en el usuario cuando de datos sensibles se trata ..
+el marco del iso27001 que podría establecer los puntos de riesgo que tienen y darle sugerencias de como prevenir</t>
+  </si>
+  <si>
+    <t>diego.martinez6455@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>​1. ​Se violó la Confidencialidad, porque un empleado se llevó datos privados de tarjetas que no debía. También falló la Integridad, ya que la empresa perdió el control sobre la autenticidad de esa información al ser extraída sin permiso.
+​2. El Mínimo privilegio, porque los desarrolladores no necesitaban acceso total a la base de datos real solo para corregir errores
+3. ​Recomendaría CIS Controls porque es el mejor inicio porque son pasos muy prácticos y directos que ayudan a limpiar la higiene básica</t>
+  </si>
+  <si>
+    <t>isis.delavega5053@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>85 / 110</t>
+  </si>
+  <si>
+    <t>Confidencialidad, porque información bancaria fue usada de forma indebida por parte de un es empleado; el Zero trust hubiera funcionados para el caso, con el mínimo privilegio que se le otorgara a los empleados seria ya una mitigación. NIST, por ser un marco que funciona para múltiples tipos de organizaciones y que es adaptable a lo que es en este caso una startup financiera, se debe tener en cuenta que el presupuesto para la implementación de ciertas tecnologías es bastante elevado para aquellos que van estableciéndose en el mercado.</t>
+  </si>
+  <si>
+    <t>maria.perez9710@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>62 / 110</t>
+  </si>
+  <si>
+    <t>a) NIST CSF 2.0</t>
+  </si>
+  <si>
+    <t>Directamente se violo la confidencialidad y la integridad de los datos, porque si bien era un empleado de la empresa, el pudo ingresar fácilmente a esta información sin problema alguno. | Al momento de crear los perfiles de los trabajadores, asignar permisos diferentes de acuerdo a su puesto de trabajo, ya que por ejemplo, alguien de mkt no tiene que ver información de finanzas; con esto hay un mayor control con información sensible. | El NIST, porque tiene una referencia de marcos de seguridad o recomendaciones de como mejorar los niveles de seguridad, de configuración, casi casi es un paso a paso.</t>
+  </si>
+  <si>
+    <t>rogelio.acosta4009@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>CIA Triad: Se violó la Confidencialidad, ya que un usuario accedió y extrajo datos privados sin autorización para ese fin.
+Principio de diseño: El Mínimo privilegio, pues los desarrolladores nunca debieron tener acceso a la base de datos de producción real.
+Marco de seguridad: CIS Controls v8 (IG1), porque es práctico, prescriptivo y se enfoca en la higiene básica necesaria para startups</t>
+  </si>
+  <si>
+    <t>diego.ibarra5066@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>96 / 110</t>
+  </si>
+  <si>
+    <t>-Confidencialidad, los datos no fueron protegidos debidamente. 
+-Que no se tenga libre acceso a la base de datos y que no se puedan conectar a fuentes de almacenamiento externo al del equipo así como limitaciones en la red para evitar que se envíen por paginas y aplicaciones externas no autorizadas.
+-Recomendaría que implementen un MFA con el cliente, que cuando el cliente necesite ayuda con su tarjeta, para acceder a su información le llegue un código y se lo proporcione al operador, eso y las recomendaciones de la respuesta anterior.</t>
+  </si>
+  <si>
+    <t>25/03/2026 10:05:43</t>
+  </si>
+  <si>
+    <t>tania.gonzalez9708@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>Considero que 2 pilares de la CIA fueron violados, la Confidencialidad y la integridad, como no tuvieron los controles requeridos y la integridad por el hecho de poder manipular sus datos para realizar los cargos. El mínimo privilegio, los empleados solo deben acceder a la información mínima para realizar su trabajo, le recomiendo realizar la autenticación multifactor dependiendo la información a la que se pretende acceder.</t>
+  </si>
+  <si>
+    <t>alvaro.rojas6455@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>77 / 110</t>
+  </si>
+  <si>
+    <t>La confidencialidad solamente por qué todo siguió disponible y no se modificaron pero si se usaron las tarjetas
+El mínimo privilegio hubiera sido una opción
+Creo que nist estaría bien para comenzar con algo sencillo pero fuerte que pueda brincar conceptos básicos como el mínimo privilegio y confianza cero</t>
+  </si>
+  <si>
+    <t>karol.avalos6455@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>66 / 110</t>
+  </si>
+  <si>
+    <t>d) PROTECT — ¿Cómo prevenimos incidentes?</t>
+  </si>
+  <si>
+    <t>Se violo la confidencialidad porque sus datos fueron bancarios expuestos y no aplicaron el mínimo privilegio, la integridad porque les hicieron cargos entonces no se quedaron íntegros ya que fueron modificados, diseño de arquitectura, y yo diría que el NIST ya que el Iso27001 es ya para algo más internacional entonces le recomiendo este para ir empezar con la seguridad de la empresa ya que tiene los marcos necesarios para que protejan mejor su información.</t>
+  </si>
+  <si>
+    <t>cristian.garay1054@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>Fue violada la confidencialidad y la integridad de los datos.
+Seria el minimo privilegio que estableceria que cada usuario debe tener acceso a la informacion y al sistema solo lo necesario para trabajar, controles de acceso, gestion de identidades, clasificacion de informacion, etc.
+Se recomendaria NITS por practico y adaptable o ISO 27001 por ser estandar certificable y muy reconocido.</t>
+  </si>
+  <si>
+    <t>gabriela.arias0485@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>fueron expuestos la integridad y disponibilidad</t>
+  </si>
+  <si>
+    <t>victor.hernandez6453@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>99 / 110</t>
+  </si>
+  <si>
+    <t>Confidencialidad e Integridad: Se violó la confidencialidad porque los datos fueron exfiltrados. También se afectó la integridad, ya que el desarrollador "corrompió" la confianza del sistema y alteró el flujo normal de la base de datos al realizar una descarga masiva no autorizada.
+Defensa en Profundidad: Si la empresa hubiera implementado este principio, habrían tenido varios firewalls internos que habrían bloqueado la conexión del desarrollador hacia los servidores de producción, impidiendo que llegara hasta los datos.
+NIST CSF: Les recomendaría este marco porque, al ser una empresa de tecnología financiera (fintech), es el estándar obligatorio por ley que deben cumplir para poder operar y procesar pagos con tarjeta de crédito de forma legal.</t>
+  </si>
+  <si>
+    <t>tabata.hernandez8735@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>- Se violaron la confidencialidad (porque ya un tercero tiene acceso a ellos) y la integridad porque nada nos garantiza que no se hayan modificado o eliminado algunos datos. El principio que nos habría ayudado sería el Privilegio mínimo (para que no tuviera más accesos de los necesarios y la segregación de funciones.</t>
+  </si>
+  <si>
+    <t>25/03/2026 10:51:10</t>
+  </si>
+  <si>
+    <t>israel.pimentel6454@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>108 / 110</t>
+  </si>
+  <si>
+    <t>La confidencialidad se rompio, ya que el desarrollador saco la informacion sin permiso.
+Por lo visto solo la confidencialidad fue la afectada, porque no menciona alguna alteracion en la empresa o funcionamiento o alguna cosa mas.
+Considero que es fundamental implementar políticas internas de seguridad y acuerdos de confidencialidad que restrinjan el acceso a la información</t>
+  </si>
+  <si>
+    <t>Puntuación Provisional</t>
+  </si>
+  <si>
+    <t>Puntos Extra Participación</t>
+  </si>
+  <si>
+    <t>Puntos Extra Examen</t>
+  </si>
+  <si>
+    <t>Nombre de Alumno</t>
+  </si>
+  <si>
+    <t>GONZALEZ CUELLAR EDGAR OSWALDO</t>
+  </si>
+  <si>
+    <t>MARTINEZ DURAN MAHONRI MORIANC</t>
+  </si>
+  <si>
+    <t>MUÑOZ RIVAS JOSHUA</t>
+  </si>
+  <si>
+    <t>FREGOSO SANCHEZ PAOLA</t>
+  </si>
+  <si>
+    <t>LAZOS CRUZ ALLISON</t>
+  </si>
+  <si>
+    <t>FRANCO ARELLANO DAPHNE WENDOLYN</t>
+  </si>
+  <si>
+    <t>CARCAÑO AGUAYO ANDREA LISSETH</t>
+  </si>
+  <si>
+    <t>GERALDO RUBIO JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>REYES OLMEDO CHRISTIAN ALEJA</t>
+  </si>
+  <si>
+    <t>GONZALEZ MEDRANO LILIANA ARALI</t>
+  </si>
+  <si>
+    <t>PONCE RAMIREZ JORGE ALBERTO</t>
+  </si>
+  <si>
+    <t>ZARAGOZA BRAMBILA FABIAN ISAI</t>
+  </si>
+  <si>
+    <t>GOMEZ CASTORENA ERICK JOSUE</t>
+  </si>
+  <si>
+    <t>MARTINEZ GUTIERREZ DIEGO EUGENIO</t>
+  </si>
+  <si>
+    <t>DE LA VEGA SANCHEZ ISIS KAROL</t>
+  </si>
+  <si>
+    <t>PEREZ GOMEZ MARIA ANDREA</t>
+  </si>
+  <si>
+    <t>ACOSTA SANDOVAL ROGELIO ESAU</t>
+  </si>
+  <si>
+    <t>IBARRA GRACIA DIEGO DAVID</t>
+  </si>
+  <si>
+    <t>GONZALEZ CALVILLO TANIA MARIA</t>
+  </si>
+  <si>
+    <t>ROJAS BOBADILLA ALVARO ARTURO</t>
+  </si>
+  <si>
+    <t>AVALOS RODRIGUEZ KAROL GUADALUPE</t>
+  </si>
+  <si>
+    <t>GARAY GUZMAN CRISTIAN RENE</t>
+  </si>
+  <si>
+    <t>ARIAS CASTELLON GABRIELA ESPERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ VILLANUEVA VICTOR DANIEL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ VENEGAS TABATA CRISTINA</t>
+  </si>
+  <si>
+    <t>PIMENTEL MELGOZA ISRAEL RICARDO</t>
   </si>
 </sst>
 </file>
@@ -493,7 +1002,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,8 +1068,30 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -627,8 +1158,62 @@
         <bgColor rgb="FFF2F7F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF237A44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFF9E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF2F7F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B3F86"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -664,11 +1249,228 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF5B3F86"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF5B3F86"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF5B3F86"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -729,6 +1531,37 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -746,6 +1579,76 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -845,6 +1748,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1024,109 +1931,139 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{4672BD36-4CC6-407E-9D47-9DA25B605694}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;cd3cee39-8064-473a-b1ea-18d85a69773c&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AP35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="37" width="4.42578125" customWidth="1"/>
-    <col min="38" max="39" width="7" customWidth="1"/>
-    <col min="40" max="40" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="4.140625" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" customWidth="1"/>
+    <col min="7" max="17" width="4.42578125" customWidth="1"/>
+    <col min="18" max="18" width="7" customWidth="1"/>
+    <col min="19" max="32" width="4.42578125" customWidth="1"/>
+    <col min="33" max="33" width="4.42578125" style="26" customWidth="1"/>
+    <col min="34" max="38" width="4.42578125" customWidth="1"/>
+    <col min="39" max="40" width="7" customWidth="1"/>
+    <col min="41" max="41" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="26"/>
-      <c r="AL1" s="26"/>
-      <c r="AM1" s="26"/>
-      <c r="AN1" s="26"/>
-    </row>
-    <row r="2" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="37"/>
+      <c r="AM1" s="37"/>
+      <c r="AN1" s="37"/>
+      <c r="AO1" s="37"/>
+    </row>
+    <row r="2" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="27"/>
-      <c r="AJ2" s="27"/>
-      <c r="AK2" s="27"/>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="27"/>
-    </row>
-    <row r="3" spans="1:40" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38"/>
+      <c r="AM2" s="38"/>
+      <c r="AN2" s="38"/>
+      <c r="AO2" s="38"/>
+    </row>
+    <row r="3" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1140,295 +2077,300 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="34"/>
+      <c r="I3" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="22"/>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="33"/>
+      <c r="K3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="23"/>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="34"/>
+      <c r="M3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="22"/>
-      <c r="N3" s="23" t="s">
+      <c r="N3" s="33"/>
+      <c r="O3" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="23"/>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="34"/>
+      <c r="Q3" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="23" t="s">
+      <c r="R3" s="33"/>
+      <c r="S3" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="23"/>
-      <c r="T3" s="22" t="s">
+      <c r="T3" s="34"/>
+      <c r="U3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="22"/>
-      <c r="V3" s="23" t="s">
+      <c r="V3" s="33"/>
+      <c r="W3" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="23"/>
-      <c r="X3" s="22" t="s">
+      <c r="X3" s="34"/>
+      <c r="Y3" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="23" t="s">
+      <c r="Z3" s="33"/>
+      <c r="AA3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="AA3" s="23"/>
-      <c r="AB3" s="22" t="s">
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="23" t="s">
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="AE3" s="23"/>
-      <c r="AF3" s="22" t="s">
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="23" t="s">
+      <c r="AH3" s="33"/>
+      <c r="AI3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="AI3" s="23"/>
-      <c r="AJ3" s="22" t="s">
+      <c r="AJ3" s="34"/>
+      <c r="AK3" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="4" t="s">
+      <c r="AL3" s="33"/>
+      <c r="AM3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AM3" s="4" t="s">
+      <c r="AN3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AN3" s="4" t="s">
+      <c r="AO3" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:40" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="P4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="R4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="S4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="T4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="W4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="X4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Y4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="Z4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA4" s="7" t="s">
+      <c r="AB4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AC4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AC4" s="7" t="s">
+      <c r="AD4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AD4" s="6" t="s">
+      <c r="AE4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AE4" s="7" t="s">
+      <c r="AF4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AG4" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="AG4" s="7" t="s">
+      <c r="AH4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH4" s="6" t="s">
+      <c r="AI4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AI4" s="7" t="s">
+      <c r="AJ4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AJ4" s="6" t="s">
+      <c r="AK4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AK4" s="7" t="s">
+      <c r="AL4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AL4" s="8"/>
       <c r="AM4" s="8"/>
       <c r="AN4" s="8"/>
-    </row>
-    <row r="5" spans="1:40" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO4" s="8"/>
+    </row>
+    <row r="5" spans="1:41" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5"/>
+      <c r="G5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="P5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="Q5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="Q5" s="7" t="s">
+      <c r="R5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="7" t="s">
+      <c r="T5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="U5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="U5" s="7" t="s">
+      <c r="V5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="W5" s="7" t="s">
+      <c r="X5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="Y5" s="7" t="s">
+      <c r="Z5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="Z5" s="6" t="s">
+      <c r="AA5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AA5" s="7" t="s">
+      <c r="AB5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AB5" s="6" t="s">
+      <c r="AC5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AC5" s="7" t="s">
+      <c r="AD5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AD5" s="6" t="s">
+      <c r="AE5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AE5" s="7" t="s">
+      <c r="AF5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="AF5" s="6" t="s">
+      <c r="AG5" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="AG5" s="7" t="s">
+      <c r="AH5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AH5" s="6" t="s">
+      <c r="AI5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AI5" s="7" t="s">
+      <c r="AJ5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="AJ5" s="6" t="s">
+      <c r="AK5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AK5" s="7" t="s">
+      <c r="AL5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AL5" s="8"/>
       <c r="AM5" s="8"/>
       <c r="AN5" s="8"/>
-    </row>
-    <row r="6" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO5" s="8"/>
+    </row>
+    <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>1</v>
       </c>
@@ -1442,8 +2384,9 @@
         <v>61</v>
       </c>
       <c r="E6" s="11"/>
-      <c r="F6" s="19" t="s">
-        <v>145</v>
+      <c r="F6" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B6&amp;" "&amp;C6,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>145</v>
@@ -1491,10 +2434,10 @@
         <v>145</v>
       </c>
       <c r="V6" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W6" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X6" s="19" t="s">
         <v>146</v>
@@ -1502,36 +2445,43 @@
       <c r="Y6" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z6" s="12" t="s">
-        <v>145</v>
+      <c r="Z6" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA6" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
+      <c r="AB6" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC6" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD6" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
-      <c r="AG6" s="12"/>
+      <c r="AG6" s="23"/>
       <c r="AH6" s="12"/>
       <c r="AI6" s="12"/>
       <c r="AJ6" s="12"/>
       <c r="AK6" s="12"/>
-      <c r="AL6" s="13">
-        <f t="shared" ref="AL6:AL32" si="0">COUNTIF(F6,"A")+COUNTIF(G6,"A")+COUNTIF(H6,"A")+COUNTIF(I6,"A")+COUNTIF(J6,"A")+COUNTIF(K6,"A")+COUNTIF(L6,"A")+COUNTIF(M6,"A")+COUNTIF(N6,"A")+COUNTIF(O6,"A")+COUNTIF(P6,"A")+COUNTIF(Q6,"A")+COUNTIF(R6,"A")+COUNTIF(S6,"A")+COUNTIF(T6,"A")+COUNTIF(U6,"A")+COUNTIF(V6,"A")+COUNTIF(W6,"A")+COUNTIF(X6,"A")+COUNTIF(Y6,"A")+COUNTIF(Z6,"A")+COUNTIF(AA6,"A")+COUNTIF(AB6,"A")+COUNTIF(AC6,"A")+COUNTIF(AD6,"A")+COUNTIF(AE6,"A")+COUNTIF(AF6,"A")+COUNTIF(AG6,"A")+COUNTIF(AH6,"A")+COUNTIF(AI6,"A")+COUNTIF(AJ6,"A")+COUNTIF(AK6,"A")</f>
-        <v>18</v>
-      </c>
-      <c r="AM6" s="14">
-        <f t="shared" ref="AM6:AM32" si="1">COUNTIF(F6,"F")+COUNTIF(G6,"F")+COUNTIF(H6,"F")+COUNTIF(I6,"F")+COUNTIF(J6,"F")+COUNTIF(K6,"F")+COUNTIF(L6,"F")+COUNTIF(M6,"F")+COUNTIF(N6,"F")+COUNTIF(O6,"F")+COUNTIF(P6,"F")+COUNTIF(Q6,"F")+COUNTIF(R6,"F")+COUNTIF(S6,"F")+COUNTIF(T6,"F")+COUNTIF(U6,"F")+COUNTIF(V6,"F")+COUNTIF(W6,"F")+COUNTIF(X6,"F")+COUNTIF(Y6,"F")+COUNTIF(Z6,"F")+COUNTIF(AA6,"F")+COUNTIF(AB6,"F")+COUNTIF(AC6,"F")+COUNTIF(AD6,"F")+COUNTIF(AE6,"F")+COUNTIF(AF6,"F")+COUNTIF(AG6,"F")+COUNTIF(AH6,"F")+COUNTIF(AI6,"F")+COUNTIF(AJ6,"F")+COUNTIF(AK6,"F")</f>
+      <c r="AL6" s="12"/>
+      <c r="AM6" s="13">
+        <f t="shared" ref="AM6:AM32" si="0">COUNTIF(G6,"A")+COUNTIF(H6,"A")+COUNTIF(I6,"A")+COUNTIF(J6,"A")+COUNTIF(K6,"A")+COUNTIF(L6,"A")+COUNTIF(M6,"A")+COUNTIF(N6,"A")+COUNTIF(O6,"A")+COUNTIF(P6,"A")+COUNTIF(Q6,"A")+COUNTIF(R6,"A")+COUNTIF(S6,"A")+COUNTIF(T6,"A")+COUNTIF(U6,"A")+COUNTIF(V6,"A")+COUNTIF(W6,"A")+COUNTIF(X6,"A")+COUNTIF(Y6,"A")+COUNTIF(Z6,"A")+COUNTIF(AA6,"A")+COUNTIF(AB6,"A")+COUNTIF(AC6,"A")+COUNTIF(AD6,"A")+COUNTIF(AE6,"A")+COUNTIF(AF6,"A")+COUNTIF(AG6,"A")+COUNTIF(AH6,"A")+COUNTIF(AI6,"A")+COUNTIF(AJ6,"A")+COUNTIF(AK6,"A")+COUNTIF(AL6,"A")</f>
+        <v>21</v>
+      </c>
+      <c r="AN6" s="14">
+        <f t="shared" ref="AN6:AN32" si="1">COUNTIF(G6,"F")+COUNTIF(H6,"F")+COUNTIF(I6,"F")+COUNTIF(J6,"F")+COUNTIF(K6,"F")+COUNTIF(L6,"F")+COUNTIF(M6,"F")+COUNTIF(N6,"F")+COUNTIF(O6,"F")+COUNTIF(P6,"F")+COUNTIF(Q6,"F")+COUNTIF(R6,"F")+COUNTIF(S6,"F")+COUNTIF(T6,"F")+COUNTIF(U6,"F")+COUNTIF(V6,"F")+COUNTIF(W6,"F")+COUNTIF(X6,"F")+COUNTIF(Y6,"F")+COUNTIF(Z6,"F")+COUNTIF(AA6,"F")+COUNTIF(AB6,"F")+COUNTIF(AC6,"F")+COUNTIF(AD6,"F")+COUNTIF(AE6,"F")+COUNTIF(AF6,"F")+COUNTIF(AG6,"F")+COUNTIF(AH6,"F")+COUNTIF(AI6,"F")+COUNTIF(AJ6,"F")+COUNTIF(AK6,"F")+COUNTIF(AL6,"F")</f>
         <v>0</v>
       </c>
-      <c r="AN6" s="15">
-        <f t="shared" ref="AN6:AN32" si="2">IF(AL6=0,"",AL6/32)</f>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO6" s="15">
+        <f t="shared" ref="AO6:AO32" si="2">IF(AM6=0,"",AM6/32)</f>
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>2</v>
       </c>
@@ -1545,8 +2495,9 @@
         <v>64</v>
       </c>
       <c r="E7" s="18"/>
-      <c r="F7" s="19" t="s">
-        <v>145</v>
+      <c r="F7" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B7&amp;" "&amp;C7,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>4.3</v>
       </c>
       <c r="G7" s="19" t="s">
         <v>145</v>
@@ -1594,10 +2545,10 @@
         <v>145</v>
       </c>
       <c r="V7" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W7" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X7" s="19" t="s">
         <v>146</v>
@@ -1605,36 +2556,43 @@
       <c r="Y7" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z7" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="19"/>
+      <c r="Z7" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA7" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB7" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC7" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD7" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE7" s="19"/>
       <c r="AF7" s="19"/>
-      <c r="AG7" s="19"/>
+      <c r="AG7" s="24"/>
       <c r="AH7" s="19"/>
       <c r="AI7" s="19"/>
       <c r="AJ7" s="19"/>
       <c r="AK7" s="19"/>
-      <c r="AL7" s="13">
+      <c r="AL7" s="19"/>
+      <c r="AM7" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM7" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN7" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN7" s="15">
+      <c r="AO7" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>3</v>
       </c>
@@ -1647,9 +2605,12 @@
       <c r="D8" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="19" t="s">
-        <v>145</v>
+      <c r="E8" s="11">
+        <v>1</v>
+      </c>
+      <c r="F8" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B8&amp;" "&amp;C8,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>3.3</v>
       </c>
       <c r="G8" s="19" t="s">
         <v>145</v>
@@ -1697,10 +2658,10 @@
         <v>145</v>
       </c>
       <c r="V8" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W8" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X8" s="19" t="s">
         <v>146</v>
@@ -1708,36 +2669,43 @@
       <c r="Y8" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z8" s="12" t="s">
-        <v>145</v>
+      <c r="Z8" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA8" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
+      <c r="AB8" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC8" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD8" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE8" s="12"/>
       <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
+      <c r="AG8" s="23"/>
       <c r="AH8" s="12"/>
       <c r="AI8" s="12"/>
       <c r="AJ8" s="12"/>
       <c r="AK8" s="12"/>
-      <c r="AL8" s="13">
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM8" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN8" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN8" s="15">
+      <c r="AO8" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>4</v>
       </c>
@@ -1751,8 +2719,9 @@
         <v>70</v>
       </c>
       <c r="E9" s="18"/>
-      <c r="F9" s="19" t="s">
-        <v>145</v>
+      <c r="F9" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B9&amp;" "&amp;C9,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>145</v>
@@ -1800,10 +2769,10 @@
         <v>145</v>
       </c>
       <c r="V9" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W9" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X9" s="19" t="s">
         <v>146</v>
@@ -1811,36 +2780,43 @@
       <c r="Y9" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z9" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA9" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
+      <c r="Z9" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB9" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD9" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE9" s="19"/>
       <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
+      <c r="AG9" s="24"/>
       <c r="AH9" s="19"/>
       <c r="AI9" s="19"/>
       <c r="AJ9" s="19"/>
       <c r="AK9" s="19"/>
-      <c r="AL9" s="13">
+      <c r="AL9" s="19"/>
+      <c r="AM9" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM9" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN9" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="15">
+      <c r="AO9" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>5</v>
       </c>
@@ -1856,8 +2832,9 @@
       <c r="E10" s="11">
         <v>1</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>145</v>
+      <c r="F10" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B10&amp;" "&amp;C10,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>4.3</v>
       </c>
       <c r="G10" s="19" t="s">
         <v>145</v>
@@ -1905,10 +2882,10 @@
         <v>145</v>
       </c>
       <c r="V10" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W10" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X10" s="19" t="s">
         <v>146</v>
@@ -1916,36 +2893,43 @@
       <c r="Y10" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z10" s="12" t="s">
-        <v>145</v>
+      <c r="Z10" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA10" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="12"/>
+      <c r="AB10" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC10" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD10" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE10" s="12"/>
       <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
+      <c r="AG10" s="23"/>
       <c r="AH10" s="12"/>
       <c r="AI10" s="12"/>
       <c r="AJ10" s="12"/>
       <c r="AK10" s="12"/>
-      <c r="AL10" s="13">
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM10" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN10" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN10" s="15">
+      <c r="AO10" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>6</v>
       </c>
@@ -1959,8 +2943,9 @@
         <v>76</v>
       </c>
       <c r="E11" s="18"/>
-      <c r="F11" s="19" t="s">
-        <v>145</v>
+      <c r="F11" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B11&amp;" "&amp;C11,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>0</v>
       </c>
       <c r="G11" s="19" t="s">
         <v>145</v>
@@ -2008,10 +2993,10 @@
         <v>145</v>
       </c>
       <c r="V11" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W11" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X11" s="19" t="s">
         <v>146</v>
@@ -2019,36 +3004,43 @@
       <c r="Y11" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z11" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
+      <c r="Z11" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA11" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB11" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC11" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD11" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE11" s="19"/>
       <c r="AF11" s="19"/>
-      <c r="AG11" s="19"/>
+      <c r="AG11" s="24"/>
       <c r="AH11" s="19"/>
       <c r="AI11" s="19"/>
       <c r="AJ11" s="19"/>
       <c r="AK11" s="19"/>
-      <c r="AL11" s="13">
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM11" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN11" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN11" s="15">
+      <c r="AO11" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>7</v>
       </c>
@@ -2064,8 +3056,9 @@
       <c r="E12" s="11">
         <v>1</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>145</v>
+      <c r="F12" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B12&amp;" "&amp;C12,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G12" s="19" t="s">
         <v>145</v>
@@ -2113,10 +3106,10 @@
         <v>145</v>
       </c>
       <c r="V12" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W12" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X12" s="19" t="s">
         <v>146</v>
@@ -2124,36 +3117,43 @@
       <c r="Y12" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z12" s="12" t="s">
-        <v>145</v>
+      <c r="Z12" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA12" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB12" s="12"/>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="12"/>
+      <c r="AB12" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC12" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD12" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE12" s="12"/>
       <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
+      <c r="AG12" s="23"/>
       <c r="AH12" s="12"/>
       <c r="AI12" s="12"/>
       <c r="AJ12" s="12"/>
       <c r="AK12" s="12"/>
-      <c r="AL12" s="13">
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM12" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN12" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="15">
+      <c r="AO12" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>8</v>
       </c>
@@ -2167,8 +3167,9 @@
         <v>82</v>
       </c>
       <c r="E13" s="18"/>
-      <c r="F13" s="19" t="s">
-        <v>145</v>
+      <c r="F13" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B13&amp;" "&amp;C13,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G13" s="19" t="s">
         <v>145</v>
@@ -2216,10 +3217,10 @@
         <v>145</v>
       </c>
       <c r="V13" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W13" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X13" s="19" t="s">
         <v>146</v>
@@ -2227,36 +3228,43 @@
       <c r="Y13" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z13" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA13" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
+      <c r="Z13" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA13" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB13" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC13" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD13" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
-      <c r="AG13" s="19"/>
+      <c r="AG13" s="24"/>
       <c r="AH13" s="19"/>
       <c r="AI13" s="19"/>
       <c r="AJ13" s="19"/>
       <c r="AK13" s="19"/>
-      <c r="AL13" s="13">
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM13" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN13" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN13" s="15">
+      <c r="AO13" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="14" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>9</v>
       </c>
@@ -2270,8 +3278,9 @@
         <v>85</v>
       </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="19" t="s">
-        <v>145</v>
+      <c r="F14" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B14&amp;" "&amp;C14,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G14" s="19" t="s">
         <v>145</v>
@@ -2319,10 +3328,10 @@
         <v>145</v>
       </c>
       <c r="V14" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W14" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X14" s="19" t="s">
         <v>146</v>
@@ -2330,36 +3339,43 @@
       <c r="Y14" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z14" s="12" t="s">
-        <v>145</v>
+      <c r="Z14" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB14" s="12"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="12"/>
+      <c r="AB14" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC14" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD14" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE14" s="12"/>
       <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
+      <c r="AG14" s="23"/>
       <c r="AH14" s="12"/>
       <c r="AI14" s="12"/>
       <c r="AJ14" s="12"/>
       <c r="AK14" s="12"/>
-      <c r="AL14" s="13">
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM14" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN14" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="15">
+      <c r="AO14" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>10</v>
       </c>
@@ -2375,8 +3391,9 @@
       <c r="E15" s="18">
         <v>1</v>
       </c>
-      <c r="F15" s="19" t="s">
-        <v>145</v>
+      <c r="F15" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B15&amp;" "&amp;C15,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>145</v>
@@ -2424,10 +3441,10 @@
         <v>145</v>
       </c>
       <c r="V15" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W15" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X15" s="19" t="s">
         <v>146</v>
@@ -2435,36 +3452,43 @@
       <c r="Y15" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z15" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA15" s="19" t="s">
+      <c r="Z15" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA15" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB15" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="19"/>
-      <c r="AD15" s="19"/>
+      <c r="AC15" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD15" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
-      <c r="AG15" s="19"/>
+      <c r="AG15" s="24"/>
       <c r="AH15" s="19"/>
       <c r="AI15" s="19"/>
       <c r="AJ15" s="19"/>
       <c r="AK15" s="19"/>
-      <c r="AL15" s="13">
+      <c r="AL15" s="19"/>
+      <c r="AM15" s="13">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AM15" s="14">
+        <v>20</v>
+      </c>
+      <c r="AN15" s="14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AN15" s="15">
+      <c r="AO15" s="15">
         <f t="shared" si="2"/>
-        <v>0.53125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>11</v>
       </c>
@@ -2478,8 +3502,9 @@
         <v>91</v>
       </c>
       <c r="E16" s="11"/>
-      <c r="F16" s="19" t="s">
-        <v>145</v>
+      <c r="F16" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B16&amp;" "&amp;C16,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>2.7</v>
       </c>
       <c r="G16" s="19" t="s">
         <v>145</v>
@@ -2527,10 +3552,10 @@
         <v>145</v>
       </c>
       <c r="V16" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W16" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X16" s="19" t="s">
         <v>146</v>
@@ -2538,36 +3563,43 @@
       <c r="Y16" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z16" s="12" t="s">
-        <v>145</v>
+      <c r="Z16" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA16" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB16" s="12"/>
-      <c r="AC16" s="12"/>
-      <c r="AD16" s="12"/>
+      <c r="AB16" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC16" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD16" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE16" s="12"/>
       <c r="AF16" s="12"/>
-      <c r="AG16" s="12"/>
+      <c r="AG16" s="23"/>
       <c r="AH16" s="12"/>
       <c r="AI16" s="12"/>
       <c r="AJ16" s="12"/>
       <c r="AK16" s="12"/>
-      <c r="AL16" s="13">
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM16" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN16" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="15">
+      <c r="AO16" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="17" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>12</v>
       </c>
@@ -2581,8 +3613,9 @@
         <v>94</v>
       </c>
       <c r="E17" s="18"/>
-      <c r="F17" s="19" t="s">
-        <v>145</v>
+      <c r="F17" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B17&amp;" "&amp;C17,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G17" s="19" t="s">
         <v>145</v>
@@ -2630,10 +3663,10 @@
         <v>145</v>
       </c>
       <c r="V17" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W17" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X17" s="19" t="s">
         <v>146</v>
@@ -2641,36 +3674,43 @@
       <c r="Y17" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z17" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA17" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="19"/>
+      <c r="Z17" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA17" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB17" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC17" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD17" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE17" s="19"/>
       <c r="AF17" s="19"/>
-      <c r="AG17" s="19"/>
+      <c r="AG17" s="24"/>
       <c r="AH17" s="19"/>
       <c r="AI17" s="19"/>
       <c r="AJ17" s="19"/>
       <c r="AK17" s="19"/>
-      <c r="AL17" s="13">
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM17" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN17" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="15">
+      <c r="AO17" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>13</v>
       </c>
@@ -2684,8 +3724,9 @@
         <v>97</v>
       </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="19" t="s">
-        <v>145</v>
+      <c r="F18" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B18&amp;" "&amp;C18,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>4.7</v>
       </c>
       <c r="G18" s="19" t="s">
         <v>145</v>
@@ -2733,10 +3774,10 @@
         <v>145</v>
       </c>
       <c r="V18" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W18" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X18" s="19" t="s">
         <v>146</v>
@@ -2744,36 +3785,43 @@
       <c r="Y18" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z18" s="12" t="s">
-        <v>145</v>
+      <c r="Z18" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA18" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB18" s="12"/>
-      <c r="AC18" s="12"/>
-      <c r="AD18" s="12"/>
+      <c r="AB18" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC18" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD18" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE18" s="12"/>
       <c r="AF18" s="12"/>
-      <c r="AG18" s="12"/>
+      <c r="AG18" s="23"/>
       <c r="AH18" s="12"/>
       <c r="AI18" s="12"/>
       <c r="AJ18" s="12"/>
       <c r="AK18" s="12"/>
-      <c r="AL18" s="13">
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM18" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN18" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="15">
+      <c r="AO18" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>14</v>
       </c>
@@ -2789,8 +3837,9 @@
       <c r="E19" s="18">
         <v>1</v>
       </c>
-      <c r="F19" s="19" t="s">
-        <v>145</v>
+      <c r="F19" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B19&amp;" "&amp;C19,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G19" s="19" t="s">
         <v>145</v>
@@ -2838,10 +3887,10 @@
         <v>145</v>
       </c>
       <c r="V19" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W19" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X19" s="19" t="s">
         <v>146</v>
@@ -2849,36 +3898,43 @@
       <c r="Y19" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z19" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA19" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
+      <c r="Z19" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB19" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD19" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE19" s="19"/>
       <c r="AF19" s="19"/>
-      <c r="AG19" s="19"/>
+      <c r="AG19" s="24"/>
       <c r="AH19" s="19"/>
       <c r="AI19" s="19"/>
       <c r="AJ19" s="19"/>
       <c r="AK19" s="19"/>
-      <c r="AL19" s="13">
+      <c r="AL19" s="19"/>
+      <c r="AM19" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM19" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="15">
+      <c r="AO19" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="20" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>15</v>
       </c>
@@ -2892,8 +3948,9 @@
         <v>103</v>
       </c>
       <c r="E20" s="11"/>
-      <c r="F20" s="19" t="s">
-        <v>145</v>
+      <c r="F20" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B20&amp;" "&amp;C20,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>4.8</v>
       </c>
       <c r="G20" s="19" t="s">
         <v>145</v>
@@ -2941,10 +3998,10 @@
         <v>145</v>
       </c>
       <c r="V20" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W20" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X20" s="19" t="s">
         <v>146</v>
@@ -2952,139 +4009,157 @@
       <c r="Y20" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z20" s="12" t="s">
-        <v>145</v>
+      <c r="Z20" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA20" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB20" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="AB20" s="12"/>
-      <c r="AC20" s="12"/>
-      <c r="AD20" s="12"/>
+      <c r="AC20" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD20" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE20" s="12"/>
       <c r="AF20" s="12"/>
-      <c r="AG20" s="12"/>
+      <c r="AG20" s="23"/>
       <c r="AH20" s="12"/>
       <c r="AI20" s="12"/>
       <c r="AJ20" s="12"/>
       <c r="AK20" s="12"/>
-      <c r="AL20" s="13">
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="13">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AM20" s="14">
+        <v>20</v>
+      </c>
+      <c r="AN20" s="14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AN20" s="15">
+      <c r="AO20" s="15">
         <f t="shared" si="2"/>
-        <v>0.53125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:42" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
         <v>16</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="K21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="M21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="N21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="O21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="P21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="R21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="S21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="T21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="U21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="V21" s="19" t="s">
+      <c r="E21" s="29"/>
+      <c r="F21" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B21&amp;" "&amp;C21,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="L21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="M21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="N21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="O21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="P21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="R21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="S21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="T21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="U21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="V21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="W21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="X21" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="W21" s="19" t="s">
+      <c r="Y21" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="X21" s="19" t="s">
+      <c r="Z21" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="Y21" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z21" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA21" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB21" s="19"/>
-      <c r="AC21" s="19"/>
-      <c r="AD21" s="19"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="19"/>
-      <c r="AG21" s="19"/>
-      <c r="AH21" s="19"/>
-      <c r="AI21" s="19"/>
-      <c r="AJ21" s="19"/>
-      <c r="AK21" s="19"/>
-      <c r="AL21" s="13">
+      <c r="AA21" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB21" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC21" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD21" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="AE21" s="24"/>
+      <c r="AF21" s="24"/>
+      <c r="AG21" s="24"/>
+      <c r="AH21" s="24"/>
+      <c r="AI21" s="24"/>
+      <c r="AJ21" s="24"/>
+      <c r="AK21" s="24"/>
+      <c r="AL21" s="24"/>
+      <c r="AM21" s="30">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM21" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN21" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="15">
+      <c r="AO21" s="32">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+      <c r="AP21" s="26" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>17</v>
       </c>
@@ -3098,8 +4173,9 @@
         <v>109</v>
       </c>
       <c r="E22" s="11"/>
-      <c r="F22" s="19" t="s">
-        <v>145</v>
+      <c r="F22" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B22&amp;" "&amp;C22,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>4.8</v>
       </c>
       <c r="G22" s="19" t="s">
         <v>145</v>
@@ -3147,10 +4223,10 @@
         <v>145</v>
       </c>
       <c r="V22" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W22" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X22" s="19" t="s">
         <v>146</v>
@@ -3158,36 +4234,43 @@
       <c r="Y22" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z22" s="12" t="s">
-        <v>145</v>
+      <c r="Z22" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA22" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB22" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="AB22" s="12"/>
-      <c r="AC22" s="12"/>
-      <c r="AD22" s="12"/>
+      <c r="AC22" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD22" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE22" s="12"/>
       <c r="AF22" s="12"/>
-      <c r="AG22" s="12"/>
+      <c r="AG22" s="23"/>
       <c r="AH22" s="12"/>
       <c r="AI22" s="12"/>
       <c r="AJ22" s="12"/>
       <c r="AK22" s="12"/>
-      <c r="AL22" s="13">
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="13">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="AM22" s="14">
+        <v>20</v>
+      </c>
+      <c r="AN22" s="14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AN22" s="15">
+      <c r="AO22" s="15">
         <f t="shared" si="2"/>
-        <v>0.53125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>18</v>
       </c>
@@ -3201,8 +4284,9 @@
         <v>112</v>
       </c>
       <c r="E23" s="18"/>
-      <c r="F23" s="19" t="s">
-        <v>145</v>
+      <c r="F23" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B23&amp;" "&amp;C23,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G23" s="19" t="s">
         <v>145</v>
@@ -3250,10 +4334,10 @@
         <v>145</v>
       </c>
       <c r="V23" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W23" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X23" s="19" t="s">
         <v>146</v>
@@ -3261,36 +4345,43 @@
       <c r="Y23" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z23" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA23" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="19"/>
+      <c r="Z23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB23" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD23" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE23" s="19"/>
       <c r="AF23" s="19"/>
-      <c r="AG23" s="19"/>
+      <c r="AG23" s="24"/>
       <c r="AH23" s="19"/>
       <c r="AI23" s="19"/>
       <c r="AJ23" s="19"/>
       <c r="AK23" s="19"/>
-      <c r="AL23" s="13">
+      <c r="AL23" s="19"/>
+      <c r="AM23" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM23" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN23" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="15">
+      <c r="AO23" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="24" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>19</v>
       </c>
@@ -3304,8 +4395,9 @@
         <v>115</v>
       </c>
       <c r="E24" s="11"/>
-      <c r="F24" s="19" t="s">
-        <v>145</v>
+      <c r="F24" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B24&amp;" "&amp;C24,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G24" s="19" t="s">
         <v>145</v>
@@ -3353,10 +4445,10 @@
         <v>145</v>
       </c>
       <c r="V24" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W24" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X24" s="19" t="s">
         <v>146</v>
@@ -3364,36 +4456,43 @@
       <c r="Y24" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z24" s="12" t="s">
-        <v>145</v>
+      <c r="Z24" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA24" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB24" s="12"/>
-      <c r="AC24" s="12"/>
-      <c r="AD24" s="12"/>
+      <c r="AB24" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC24" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD24" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE24" s="12"/>
       <c r="AF24" s="12"/>
-      <c r="AG24" s="12"/>
+      <c r="AG24" s="23"/>
       <c r="AH24" s="12"/>
       <c r="AI24" s="12"/>
       <c r="AJ24" s="12"/>
       <c r="AK24" s="12"/>
-      <c r="AL24" s="13">
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM24" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN24" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN24" s="15">
+      <c r="AO24" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="25" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>20</v>
       </c>
@@ -3407,8 +4506,9 @@
         <v>118</v>
       </c>
       <c r="E25" s="18"/>
-      <c r="F25" s="19" t="s">
-        <v>145</v>
+      <c r="F25" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B25&amp;" "&amp;C25,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G25" s="19" t="s">
         <v>145</v>
@@ -3456,10 +4556,10 @@
         <v>145</v>
       </c>
       <c r="V25" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W25" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X25" s="19" t="s">
         <v>146</v>
@@ -3467,36 +4567,43 @@
       <c r="Y25" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z25" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA25" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="19"/>
+      <c r="Z25" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA25" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB25" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC25" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD25" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE25" s="19"/>
       <c r="AF25" s="19"/>
-      <c r="AG25" s="19"/>
+      <c r="AG25" s="24"/>
       <c r="AH25" s="19"/>
       <c r="AI25" s="19"/>
       <c r="AJ25" s="19"/>
       <c r="AK25" s="19"/>
-      <c r="AL25" s="13">
+      <c r="AL25" s="19"/>
+      <c r="AM25" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM25" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN25" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="15">
+      <c r="AO25" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="26" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>21</v>
       </c>
@@ -3510,8 +4617,9 @@
         <v>121</v>
       </c>
       <c r="E26" s="11"/>
-      <c r="F26" s="19" t="s">
-        <v>145</v>
+      <c r="F26" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B26&amp;" "&amp;C26,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G26" s="19" t="s">
         <v>145</v>
@@ -3559,10 +4667,10 @@
         <v>145</v>
       </c>
       <c r="V26" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W26" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X26" s="19" t="s">
         <v>146</v>
@@ -3570,36 +4678,43 @@
       <c r="Y26" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z26" s="12" t="s">
-        <v>145</v>
+      <c r="Z26" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA26" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB26" s="12"/>
-      <c r="AC26" s="12"/>
-      <c r="AD26" s="12"/>
+      <c r="AB26" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC26" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD26" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE26" s="12"/>
       <c r="AF26" s="12"/>
-      <c r="AG26" s="12"/>
+      <c r="AG26" s="23"/>
       <c r="AH26" s="12"/>
       <c r="AI26" s="12"/>
       <c r="AJ26" s="12"/>
       <c r="AK26" s="12"/>
-      <c r="AL26" s="13">
+      <c r="AL26" s="12"/>
+      <c r="AM26" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM26" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN26" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="15">
+      <c r="AO26" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="27" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>22</v>
       </c>
@@ -3613,8 +4728,9 @@
         <v>124</v>
       </c>
       <c r="E27" s="18"/>
-      <c r="F27" s="19" t="s">
-        <v>145</v>
+      <c r="F27" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B27&amp;" "&amp;C27,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>3.1</v>
       </c>
       <c r="G27" s="19" t="s">
         <v>145</v>
@@ -3662,10 +4778,10 @@
         <v>145</v>
       </c>
       <c r="V27" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W27" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X27" s="19" t="s">
         <v>146</v>
@@ -3673,36 +4789,43 @@
       <c r="Y27" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z27" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA27" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB27" s="19"/>
-      <c r="AC27" s="19"/>
-      <c r="AD27" s="19"/>
+      <c r="Z27" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA27" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB27" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC27" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD27" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE27" s="19"/>
       <c r="AF27" s="19"/>
-      <c r="AG27" s="19"/>
+      <c r="AG27" s="24"/>
       <c r="AH27" s="19"/>
       <c r="AI27" s="19"/>
       <c r="AJ27" s="19"/>
       <c r="AK27" s="19"/>
-      <c r="AL27" s="13">
+      <c r="AL27" s="19"/>
+      <c r="AM27" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM27" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN27" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN27" s="15">
+      <c r="AO27" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="28" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>23</v>
       </c>
@@ -3716,8 +4839,9 @@
         <v>127</v>
       </c>
       <c r="E28" s="11"/>
-      <c r="F28" s="19" t="s">
-        <v>145</v>
+      <c r="F28" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B28&amp;" "&amp;C28,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G28" s="19" t="s">
         <v>145</v>
@@ -3765,10 +4889,10 @@
         <v>145</v>
       </c>
       <c r="V28" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W28" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X28" s="19" t="s">
         <v>146</v>
@@ -3776,36 +4900,43 @@
       <c r="Y28" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z28" s="12" t="s">
-        <v>145</v>
+      <c r="Z28" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA28" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB28" s="12"/>
-      <c r="AC28" s="12"/>
-      <c r="AD28" s="12"/>
+      <c r="AB28" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC28" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD28" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE28" s="12"/>
       <c r="AF28" s="12"/>
-      <c r="AG28" s="12"/>
+      <c r="AG28" s="23"/>
       <c r="AH28" s="12"/>
       <c r="AI28" s="12"/>
       <c r="AJ28" s="12"/>
       <c r="AK28" s="12"/>
-      <c r="AL28" s="13">
+      <c r="AL28" s="12"/>
+      <c r="AM28" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM28" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN28" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN28" s="15">
+      <c r="AO28" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="29" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>24</v>
       </c>
@@ -3821,8 +4952,9 @@
       <c r="E29" s="18">
         <v>1</v>
       </c>
-      <c r="F29" s="19" t="s">
-        <v>145</v>
+      <c r="F29" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B29&amp;" "&amp;C29,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>3.2</v>
       </c>
       <c r="G29" s="19" t="s">
         <v>145</v>
@@ -3870,10 +5002,10 @@
         <v>145</v>
       </c>
       <c r="V29" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W29" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X29" s="19" t="s">
         <v>146</v>
@@ -3881,36 +5013,43 @@
       <c r="Y29" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z29" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA29" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB29" s="19"/>
-      <c r="AC29" s="19"/>
-      <c r="AD29" s="19"/>
+      <c r="Z29" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA29" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB29" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC29" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD29" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE29" s="19"/>
       <c r="AF29" s="19"/>
-      <c r="AG29" s="19"/>
+      <c r="AG29" s="24"/>
       <c r="AH29" s="19"/>
       <c r="AI29" s="19"/>
       <c r="AJ29" s="19"/>
       <c r="AK29" s="19"/>
-      <c r="AL29" s="13">
+      <c r="AL29" s="19"/>
+      <c r="AM29" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM29" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN29" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN29" s="15">
+      <c r="AO29" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="30" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>25</v>
       </c>
@@ -3926,8 +5065,9 @@
       <c r="E30" s="11">
         <v>1</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>145</v>
+      <c r="F30" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B30&amp;" "&amp;C30,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>4.5</v>
       </c>
       <c r="G30" s="19" t="s">
         <v>145</v>
@@ -3975,10 +5115,10 @@
         <v>145</v>
       </c>
       <c r="V30" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W30" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X30" s="19" t="s">
         <v>146</v>
@@ -3986,36 +5126,43 @@
       <c r="Y30" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z30" s="12" t="s">
-        <v>145</v>
+      <c r="Z30" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA30" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB30" s="12"/>
-      <c r="AC30" s="12"/>
-      <c r="AD30" s="12"/>
+      <c r="AB30" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC30" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD30" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE30" s="12"/>
       <c r="AF30" s="12"/>
-      <c r="AG30" s="12"/>
+      <c r="AG30" s="23"/>
       <c r="AH30" s="12"/>
       <c r="AI30" s="12"/>
       <c r="AJ30" s="12"/>
       <c r="AK30" s="12"/>
-      <c r="AL30" s="13">
+      <c r="AL30" s="12"/>
+      <c r="AM30" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM30" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN30" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN30" s="15">
+      <c r="AO30" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="31" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>26</v>
       </c>
@@ -4031,8 +5178,9 @@
       <c r="E31" s="18">
         <v>1</v>
       </c>
-      <c r="F31" s="19" t="s">
-        <v>145</v>
+      <c r="F31" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B31&amp;" "&amp;C31,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>3.9</v>
       </c>
       <c r="G31" s="19" t="s">
         <v>145</v>
@@ -4080,10 +5228,10 @@
         <v>145</v>
       </c>
       <c r="V31" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W31" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X31" s="19" t="s">
         <v>146</v>
@@ -4091,36 +5239,43 @@
       <c r="Y31" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z31" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA31" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB31" s="19"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="19"/>
+      <c r="Z31" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA31" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB31" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC31" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD31" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE31" s="19"/>
       <c r="AF31" s="19"/>
-      <c r="AG31" s="19"/>
+      <c r="AG31" s="24"/>
       <c r="AH31" s="19"/>
       <c r="AI31" s="19"/>
       <c r="AJ31" s="19"/>
       <c r="AK31" s="19"/>
-      <c r="AL31" s="13">
+      <c r="AL31" s="19"/>
+      <c r="AM31" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM31" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN31" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN31" s="15">
+      <c r="AO31" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="32" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>27</v>
       </c>
@@ -4136,8 +5291,9 @@
       <c r="E32" s="11">
         <v>1</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>145</v>
+      <c r="F32" s="11">
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B32&amp;" "&amp;C32,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G32" s="19" t="s">
         <v>145</v>
@@ -4185,10 +5341,10 @@
         <v>145</v>
       </c>
       <c r="V32" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W32" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X32" s="19" t="s">
         <v>146</v>
@@ -4196,49 +5352,53 @@
       <c r="Y32" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Z32" s="12" t="s">
-        <v>145</v>
+      <c r="Z32" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="AA32" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AB32" s="12"/>
-      <c r="AC32" s="12"/>
-      <c r="AD32" s="12"/>
+      <c r="AB32" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC32" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD32" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AE32" s="12"/>
       <c r="AF32" s="12"/>
-      <c r="AG32" s="12"/>
+      <c r="AG32" s="23"/>
       <c r="AH32" s="12"/>
       <c r="AI32" s="12"/>
       <c r="AJ32" s="12"/>
       <c r="AK32" s="12"/>
-      <c r="AL32" s="13">
+      <c r="AL32" s="12"/>
+      <c r="AM32" s="13">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AM32" s="14">
+        <v>21</v>
+      </c>
+      <c r="AN32" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN32" s="15">
+      <c r="AO32" s="15">
         <f t="shared" si="2"/>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="33" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="33" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="20">
-        <f t="shared" ref="F33:AK33" si="3">COUNTIF(F6:F32,"A")</f>
-        <v>27</v>
-      </c>
+      <c r="F33" s="1"/>
       <c r="G33" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="G33:AL33" si="3">COUNTIF(G6:G32,"A")</f>
         <v>27</v>
       </c>
       <c r="H33" s="20">
@@ -4299,11 +5459,11 @@
       </c>
       <c r="V33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="W33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="X33" s="20">
         <f t="shared" si="3"/>
@@ -4315,23 +5475,23 @@
       </c>
       <c r="Z33" s="20">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="20">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AC33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE33" s="20">
         <f t="shared" si="3"/>
@@ -4341,7 +5501,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG33" s="20">
+      <c r="AG33" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4361,83 +5521,93 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="5"/>
+      <c r="AL33" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AM33" s="5"/>
       <c r="AN33" s="5"/>
-    </row>
-    <row r="34" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
+      <c r="AO33" s="5"/>
+    </row>
+    <row r="34" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="25"/>
-      <c r="AD34" s="25"/>
-      <c r="AE34" s="25"/>
-      <c r="AF34" s="25"/>
-      <c r="AG34" s="25"/>
-      <c r="AH34" s="25"/>
-      <c r="AI34" s="25"/>
-      <c r="AJ34" s="25"/>
-      <c r="AK34" s="25"/>
-      <c r="AL34" s="25"/>
-      <c r="AM34" s="25"/>
-      <c r="AN34" s="25"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="36"/>
+      <c r="Y34" s="36"/>
+      <c r="Z34" s="36"/>
+      <c r="AA34" s="36"/>
+      <c r="AB34" s="36"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="36"/>
+      <c r="AE34" s="36"/>
+      <c r="AF34" s="36"/>
+      <c r="AG34" s="36"/>
+      <c r="AH34" s="36"/>
+      <c r="AI34" s="36"/>
+      <c r="AJ34" s="36"/>
+      <c r="AK34" s="36"/>
+      <c r="AL34" s="36"/>
+      <c r="AM34" s="36"/>
+      <c r="AN34" s="36"/>
+      <c r="AO34" s="36"/>
+    </row>
+    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AG35" s="26" t="s">
+        <v>149</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="A2:AO2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A34:AN34"/>
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="A2:AN2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="A34:AO34"/>
   </mergeCells>
-  <conditionalFormatting sqref="AN6:AN32">
+  <conditionalFormatting sqref="AO6:AO32">
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AN6&lt;0.8</formula>
+      <formula>AO6&lt;0.8</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>AN6&gt;=0.8</formula>
+      <formula>AO6&gt;=0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4460,16 +5630,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -4511,19 +5681,19 @@
         <v>61</v>
       </c>
       <c r="E3" s="13">
-        <f>Asistencia!AL6</f>
-        <v>18</v>
+        <f>Asistencia!AM6</f>
+        <v>21</v>
       </c>
       <c r="F3" s="14">
-        <f>Asistencia!AM6</f>
+        <f>Asistencia!AN6</f>
         <v>0</v>
       </c>
       <c r="G3" s="15">
-        <f>Asistencia!AN6</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO6</f>
+        <v>0.65625</v>
       </c>
       <c r="H3" s="9" t="str">
-        <f>IF(Asistencia!AN6="","Sin datos",IF(Asistencia!AN6&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO6="","Sin datos",IF(Asistencia!AO6&gt;=0.8,"✅ Asistencia!AB6ARegular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4541,19 +5711,19 @@
         <v>64</v>
       </c>
       <c r="E4" s="13">
-        <f>Asistencia!AL7</f>
-        <v>18</v>
+        <f>Asistencia!AM7</f>
+        <v>21</v>
       </c>
       <c r="F4" s="14">
-        <f>Asistencia!AM7</f>
+        <f>Asistencia!AN7</f>
         <v>0</v>
       </c>
       <c r="G4" s="15">
-        <f>Asistencia!AN7</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO7</f>
+        <v>0.65625</v>
       </c>
       <c r="H4" s="16" t="str">
-        <f>IF(Asistencia!AN7="","Sin datos",IF(Asistencia!AN7&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO7="","Sin datos",IF(Asistencia!AO7&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4571,19 +5741,19 @@
         <v>67</v>
       </c>
       <c r="E5" s="13">
-        <f>Asistencia!AL8</f>
-        <v>18</v>
+        <f>Asistencia!AM8</f>
+        <v>21</v>
       </c>
       <c r="F5" s="14">
-        <f>Asistencia!AM8</f>
+        <f>Asistencia!AN8</f>
         <v>0</v>
       </c>
       <c r="G5" s="15">
-        <f>Asistencia!AN8</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO8</f>
+        <v>0.65625</v>
       </c>
       <c r="H5" s="9" t="str">
-        <f>IF(Asistencia!AN8="","Sin datos",IF(Asistencia!AN8&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO8="","Sin datos",IF(Asistencia!AO8&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4601,19 +5771,19 @@
         <v>70</v>
       </c>
       <c r="E6" s="13">
-        <f>Asistencia!AL9</f>
-        <v>18</v>
+        <f>Asistencia!AM9</f>
+        <v>21</v>
       </c>
       <c r="F6" s="14">
-        <f>Asistencia!AM9</f>
+        <f>Asistencia!AN9</f>
         <v>0</v>
       </c>
       <c r="G6" s="15">
-        <f>Asistencia!AN9</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO9</f>
+        <v>0.65625</v>
       </c>
       <c r="H6" s="16" t="str">
-        <f>IF(Asistencia!AN9="","Sin datos",IF(Asistencia!AN9&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO9="","Sin datos",IF(Asistencia!AO9&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4631,19 +5801,19 @@
         <v>73</v>
       </c>
       <c r="E7" s="13">
-        <f>Asistencia!AL10</f>
-        <v>18</v>
+        <f>Asistencia!AM10</f>
+        <v>21</v>
       </c>
       <c r="F7" s="14">
-        <f>Asistencia!AM10</f>
+        <f>Asistencia!AN10</f>
         <v>0</v>
       </c>
       <c r="G7" s="15">
-        <f>Asistencia!AN10</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO10</f>
+        <v>0.65625</v>
       </c>
       <c r="H7" s="9" t="str">
-        <f>IF(Asistencia!AN10="","Sin datos",IF(Asistencia!AN10&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO10="","Sin datos",IF(Asistencia!AO10&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4661,19 +5831,19 @@
         <v>76</v>
       </c>
       <c r="E8" s="13">
-        <f>Asistencia!AL11</f>
-        <v>18</v>
+        <f>Asistencia!AM11</f>
+        <v>21</v>
       </c>
       <c r="F8" s="14">
-        <f>Asistencia!AM11</f>
+        <f>Asistencia!AN11</f>
         <v>0</v>
       </c>
       <c r="G8" s="15">
-        <f>Asistencia!AN11</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO11</f>
+        <v>0.65625</v>
       </c>
       <c r="H8" s="16" t="str">
-        <f>IF(Asistencia!AN11="","Sin datos",IF(Asistencia!AN11&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO11="","Sin datos",IF(Asistencia!AO11&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4691,19 +5861,19 @@
         <v>79</v>
       </c>
       <c r="E9" s="13">
-        <f>Asistencia!AL12</f>
-        <v>18</v>
+        <f>Asistencia!AM12</f>
+        <v>21</v>
       </c>
       <c r="F9" s="14">
-        <f>Asistencia!AM12</f>
+        <f>Asistencia!AN12</f>
         <v>0</v>
       </c>
       <c r="G9" s="15">
-        <f>Asistencia!AN12</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO12</f>
+        <v>0.65625</v>
       </c>
       <c r="H9" s="9" t="str">
-        <f>IF(Asistencia!AN12="","Sin datos",IF(Asistencia!AN12&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO12="","Sin datos",IF(Asistencia!AO12&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4721,19 +5891,19 @@
         <v>82</v>
       </c>
       <c r="E10" s="13">
-        <f>Asistencia!AL13</f>
-        <v>18</v>
+        <f>Asistencia!AM13</f>
+        <v>21</v>
       </c>
       <c r="F10" s="14">
-        <f>Asistencia!AM13</f>
+        <f>Asistencia!AN13</f>
         <v>0</v>
       </c>
       <c r="G10" s="15">
-        <f>Asistencia!AN13</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO13</f>
+        <v>0.65625</v>
       </c>
       <c r="H10" s="16" t="str">
-        <f>IF(Asistencia!AN13="","Sin datos",IF(Asistencia!AN13&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO13="","Sin datos",IF(Asistencia!AO13&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4751,19 +5921,19 @@
         <v>85</v>
       </c>
       <c r="E11" s="13">
-        <f>Asistencia!AL14</f>
-        <v>18</v>
+        <f>Asistencia!AM14</f>
+        <v>21</v>
       </c>
       <c r="F11" s="14">
-        <f>Asistencia!AM14</f>
+        <f>Asistencia!AN14</f>
         <v>0</v>
       </c>
       <c r="G11" s="15">
-        <f>Asistencia!AN14</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO14</f>
+        <v>0.65625</v>
       </c>
       <c r="H11" s="9" t="str">
-        <f>IF(Asistencia!AN14="","Sin datos",IF(Asistencia!AN14&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO14="","Sin datos",IF(Asistencia!AO14&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4781,19 +5951,19 @@
         <v>88</v>
       </c>
       <c r="E12" s="13">
-        <f>Asistencia!AL15</f>
-        <v>17</v>
+        <f>Asistencia!AM15</f>
+        <v>20</v>
       </c>
       <c r="F12" s="14">
-        <f>Asistencia!AM15</f>
+        <f>Asistencia!AN15</f>
         <v>1</v>
       </c>
       <c r="G12" s="15">
-        <f>Asistencia!AN15</f>
-        <v>0.53125</v>
+        <f>Asistencia!AO15</f>
+        <v>0.625</v>
       </c>
       <c r="H12" s="16" t="str">
-        <f>IF(Asistencia!AN15="","Sin datos",IF(Asistencia!AN15&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO15="","Sin datos",IF(Asistencia!AO15&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4811,19 +5981,19 @@
         <v>91</v>
       </c>
       <c r="E13" s="13">
-        <f>Asistencia!AL16</f>
-        <v>18</v>
+        <f>Asistencia!AM16</f>
+        <v>21</v>
       </c>
       <c r="F13" s="14">
-        <f>Asistencia!AM16</f>
+        <f>Asistencia!AN16</f>
         <v>0</v>
       </c>
       <c r="G13" s="15">
-        <f>Asistencia!AN16</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO16</f>
+        <v>0.65625</v>
       </c>
       <c r="H13" s="9" t="str">
-        <f>IF(Asistencia!AN16="","Sin datos",IF(Asistencia!AN16&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO16="","Sin datos",IF(Asistencia!AO16&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4841,19 +6011,19 @@
         <v>94</v>
       </c>
       <c r="E14" s="13">
-        <f>Asistencia!AL17</f>
-        <v>18</v>
+        <f>Asistencia!AM17</f>
+        <v>21</v>
       </c>
       <c r="F14" s="14">
-        <f>Asistencia!AM17</f>
+        <f>Asistencia!AN17</f>
         <v>0</v>
       </c>
       <c r="G14" s="15">
-        <f>Asistencia!AN17</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO17</f>
+        <v>0.65625</v>
       </c>
       <c r="H14" s="16" t="str">
-        <f>IF(Asistencia!AN17="","Sin datos",IF(Asistencia!AN17&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO17="","Sin datos",IF(Asistencia!AO17&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4871,19 +6041,19 @@
         <v>97</v>
       </c>
       <c r="E15" s="13">
-        <f>Asistencia!AL18</f>
-        <v>18</v>
+        <f>Asistencia!AM18</f>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <f>Asistencia!AM18</f>
+        <f>Asistencia!AN18</f>
         <v>0</v>
       </c>
       <c r="G15" s="15">
-        <f>Asistencia!AN18</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO18</f>
+        <v>0.65625</v>
       </c>
       <c r="H15" s="9" t="str">
-        <f>IF(Asistencia!AN18="","Sin datos",IF(Asistencia!AN18&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO18="","Sin datos",IF(Asistencia!AO18&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4901,19 +6071,19 @@
         <v>100</v>
       </c>
       <c r="E16" s="13">
-        <f>Asistencia!AL19</f>
-        <v>18</v>
+        <f>Asistencia!AM19</f>
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <f>Asistencia!AM19</f>
+        <f>Asistencia!AN19</f>
         <v>0</v>
       </c>
       <c r="G16" s="15">
-        <f>Asistencia!AN19</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO19</f>
+        <v>0.65625</v>
       </c>
       <c r="H16" s="16" t="str">
-        <f>IF(Asistencia!AN19="","Sin datos",IF(Asistencia!AN19&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO19="","Sin datos",IF(Asistencia!AO19&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4931,19 +6101,19 @@
         <v>103</v>
       </c>
       <c r="E17" s="13">
-        <f>Asistencia!AL20</f>
-        <v>17</v>
+        <f>Asistencia!AM20</f>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
-        <f>Asistencia!AM20</f>
+        <f>Asistencia!AN20</f>
         <v>1</v>
       </c>
       <c r="G17" s="15">
-        <f>Asistencia!AN20</f>
-        <v>0.53125</v>
+        <f>Asistencia!AO20</f>
+        <v>0.625</v>
       </c>
       <c r="H17" s="9" t="str">
-        <f>IF(Asistencia!AN20="","Sin datos",IF(Asistencia!AN20&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO20="","Sin datos",IF(Asistencia!AO20&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4961,19 +6131,19 @@
         <v>106</v>
       </c>
       <c r="E18" s="13">
-        <f>Asistencia!AL21</f>
-        <v>18</v>
+        <f>Asistencia!AM21</f>
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <f>Asistencia!AM21</f>
+        <f>Asistencia!AN21</f>
         <v>0</v>
       </c>
       <c r="G18" s="15">
-        <f>Asistencia!AN21</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO21</f>
+        <v>0.65625</v>
       </c>
       <c r="H18" s="16" t="str">
-        <f>IF(Asistencia!AN21="","Sin datos",IF(Asistencia!AN21&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO21="","Sin datos",IF(Asistencia!AO21&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -4991,19 +6161,19 @@
         <v>109</v>
       </c>
       <c r="E19" s="13">
-        <f>Asistencia!AL22</f>
-        <v>17</v>
+        <f>Asistencia!AM22</f>
+        <v>20</v>
       </c>
       <c r="F19" s="14">
-        <f>Asistencia!AM22</f>
+        <f>Asistencia!AN22</f>
         <v>1</v>
       </c>
       <c r="G19" s="15">
-        <f>Asistencia!AN22</f>
-        <v>0.53125</v>
+        <f>Asistencia!AO22</f>
+        <v>0.625</v>
       </c>
       <c r="H19" s="9" t="str">
-        <f>IF(Asistencia!AN22="","Sin datos",IF(Asistencia!AN22&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO22="","Sin datos",IF(Asistencia!AO22&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5021,19 +6191,19 @@
         <v>112</v>
       </c>
       <c r="E20" s="13">
-        <f>Asistencia!AL23</f>
-        <v>18</v>
+        <f>Asistencia!AM23</f>
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <f>Asistencia!AM23</f>
+        <f>Asistencia!AN23</f>
         <v>0</v>
       </c>
       <c r="G20" s="15">
-        <f>Asistencia!AN23</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO23</f>
+        <v>0.65625</v>
       </c>
       <c r="H20" s="16" t="str">
-        <f>IF(Asistencia!AN23="","Sin datos",IF(Asistencia!AN23&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO23="","Sin datos",IF(Asistencia!AO23&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5051,19 +6221,19 @@
         <v>115</v>
       </c>
       <c r="E21" s="13">
-        <f>Asistencia!AL24</f>
-        <v>18</v>
+        <f>Asistencia!AM24</f>
+        <v>21</v>
       </c>
       <c r="F21" s="14">
-        <f>Asistencia!AM24</f>
+        <f>Asistencia!AN24</f>
         <v>0</v>
       </c>
       <c r="G21" s="15">
-        <f>Asistencia!AN24</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO24</f>
+        <v>0.65625</v>
       </c>
       <c r="H21" s="9" t="str">
-        <f>IF(Asistencia!AN24="","Sin datos",IF(Asistencia!AN24&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO24="","Sin datos",IF(Asistencia!AO24&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5081,19 +6251,19 @@
         <v>118</v>
       </c>
       <c r="E22" s="13">
-        <f>Asistencia!AL25</f>
-        <v>18</v>
+        <f>Asistencia!AM25</f>
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <f>Asistencia!AM25</f>
+        <f>Asistencia!AN25</f>
         <v>0</v>
       </c>
       <c r="G22" s="15">
-        <f>Asistencia!AN25</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO25</f>
+        <v>0.65625</v>
       </c>
       <c r="H22" s="16" t="str">
-        <f>IF(Asistencia!AN25="","Sin datos",IF(Asistencia!AN25&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO25="","Sin datos",IF(Asistencia!AO25&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5111,19 +6281,19 @@
         <v>121</v>
       </c>
       <c r="E23" s="13">
-        <f>Asistencia!AL26</f>
-        <v>18</v>
+        <f>Asistencia!AM26</f>
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <f>Asistencia!AM26</f>
+        <f>Asistencia!AN26</f>
         <v>0</v>
       </c>
       <c r="G23" s="15">
-        <f>Asistencia!AN26</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO26</f>
+        <v>0.65625</v>
       </c>
       <c r="H23" s="9" t="str">
-        <f>IF(Asistencia!AN26="","Sin datos",IF(Asistencia!AN26&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO26="","Sin datos",IF(Asistencia!AO26&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5141,19 +6311,19 @@
         <v>124</v>
       </c>
       <c r="E24" s="13">
-        <f>Asistencia!AL27</f>
-        <v>18</v>
+        <f>Asistencia!AM27</f>
+        <v>21</v>
       </c>
       <c r="F24" s="14">
-        <f>Asistencia!AM27</f>
+        <f>Asistencia!AN27</f>
         <v>0</v>
       </c>
       <c r="G24" s="15">
-        <f>Asistencia!AN27</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO27</f>
+        <v>0.65625</v>
       </c>
       <c r="H24" s="16" t="str">
-        <f>IF(Asistencia!AN27="","Sin datos",IF(Asistencia!AN27&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO27="","Sin datos",IF(Asistencia!AO27&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5171,19 +6341,19 @@
         <v>127</v>
       </c>
       <c r="E25" s="13">
-        <f>Asistencia!AL28</f>
-        <v>18</v>
+        <f>Asistencia!AM28</f>
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <f>Asistencia!AM28</f>
+        <f>Asistencia!AN28</f>
         <v>0</v>
       </c>
       <c r="G25" s="15">
-        <f>Asistencia!AN28</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO28</f>
+        <v>0.65625</v>
       </c>
       <c r="H25" s="9" t="str">
-        <f>IF(Asistencia!AN28="","Sin datos",IF(Asistencia!AN28&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO28="","Sin datos",IF(Asistencia!AO28&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5201,19 +6371,19 @@
         <v>130</v>
       </c>
       <c r="E26" s="13">
-        <f>Asistencia!AL29</f>
-        <v>18</v>
+        <f>Asistencia!AM29</f>
+        <v>21</v>
       </c>
       <c r="F26" s="14">
-        <f>Asistencia!AM29</f>
+        <f>Asistencia!AN29</f>
         <v>0</v>
       </c>
       <c r="G26" s="15">
-        <f>Asistencia!AN29</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO29</f>
+        <v>0.65625</v>
       </c>
       <c r="H26" s="16" t="str">
-        <f>IF(Asistencia!AN29="","Sin datos",IF(Asistencia!AN29&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO29="","Sin datos",IF(Asistencia!AO29&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5231,19 +6401,19 @@
         <v>133</v>
       </c>
       <c r="E27" s="13">
-        <f>Asistencia!AL30</f>
-        <v>18</v>
+        <f>Asistencia!AM30</f>
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <f>Asistencia!AM30</f>
+        <f>Asistencia!AN30</f>
         <v>0</v>
       </c>
       <c r="G27" s="15">
-        <f>Asistencia!AN30</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO30</f>
+        <v>0.65625</v>
       </c>
       <c r="H27" s="9" t="str">
-        <f>IF(Asistencia!AN30="","Sin datos",IF(Asistencia!AN30&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO30="","Sin datos",IF(Asistencia!AO30&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5261,19 +6431,19 @@
         <v>136</v>
       </c>
       <c r="E28" s="13">
-        <f>Asistencia!AL31</f>
-        <v>18</v>
+        <f>Asistencia!AM31</f>
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <f>Asistencia!AM31</f>
+        <f>Asistencia!AN31</f>
         <v>0</v>
       </c>
       <c r="G28" s="15">
-        <f>Asistencia!AN31</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO31</f>
+        <v>0.65625</v>
       </c>
       <c r="H28" s="16" t="str">
-        <f>IF(Asistencia!AN31="","Sin datos",IF(Asistencia!AN31&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO31="","Sin datos",IF(Asistencia!AO31&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5291,19 +6461,19 @@
         <v>139</v>
       </c>
       <c r="E29" s="13">
-        <f>Asistencia!AL32</f>
-        <v>18</v>
+        <f>Asistencia!AM32</f>
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <f>Asistencia!AM32</f>
+        <f>Asistencia!AN32</f>
         <v>0</v>
       </c>
       <c r="G29" s="15">
-        <f>Asistencia!AN32</f>
-        <v>0.5625</v>
+        <f>Asistencia!AO32</f>
+        <v>0.65625</v>
       </c>
       <c r="H29" s="9" t="str">
-        <f>IF(Asistencia!AN32="","Sin datos",IF(Asistencia!AN32&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
+        <f>IF(Asistencia!AO32="","Sin datos",IF(Asistencia!AO32&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
         <v>⚠️ En riesgo</v>
       </c>
     </row>
@@ -5314,4 +6484,2218 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B781B1C-465B-40C3-B31E-0122F766D036}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Z27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="57" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>275</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="K1" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="L1" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="M1" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="N1" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="O1" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="P1" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q1" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="R1" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="S1" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="T1" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="U1" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="V1" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="W1" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="X1" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y1" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z1" s="41" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="46">
+        <v>46106.414525462962</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="56">
+        <f>MIN(100,VALUE(TRIM(LEFT(D2,FIND("/",D2)-1))))</f>
+        <v>94</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="K2" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M2" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N2" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O2" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q2" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R2" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S2" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T2" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U2" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="V2" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="W2" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X2" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y2" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z2" s="49" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>46106.414560185185</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="56">
+        <f t="shared" ref="E3:E27" si="0">MIN(100,VALUE(TRIM(LEFT(D3,FIND("/",D3)-1))))</f>
+        <v>100</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H3" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J3" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K3" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L3" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M3" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N3" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O3" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P3" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q3" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R3" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S3" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T3" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U3" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V3" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W3" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X3" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y3" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z3" s="45" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="46">
+        <v>46106.41511574074</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J4" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="K4" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L4" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M4" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N4" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O4" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q4" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R4" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S4" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T4" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U4" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="V4" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W4" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X4" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y4" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z4" s="49" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="42">
+        <v>46106.416435185187</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="K5" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="L5" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M5" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N5" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O5" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P5" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q5" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R5" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S5" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T5" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U5" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="V5" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="W5" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X5" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y5" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z5" s="45" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="46">
+        <v>46106.416608796295</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I6" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="K6" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L6" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M6" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N6" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O6" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P6" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q6" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R6" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S6" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T6" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U6" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="V6" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W6" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X6" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y6" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z6" s="49" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="42">
+        <v>46106.417118055557</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H7" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J7" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L7" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M7" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N7" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O7" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P7" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q7" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R7" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S7" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T7" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U7" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V7" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W7" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X7" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y7" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z7" s="45" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="46">
+        <v>46106.417129629626</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>285</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L8" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M8" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N8" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O8" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P8" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q8" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R8" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S8" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T8" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U8" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="V8" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W8" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X8" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y8" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z8" s="49" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="42">
+        <v>46106.417349537034</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H9" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J9" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L9" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M9" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N9" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O9" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P9" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q9" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R9" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S9" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T9" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U9" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V9" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W9" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X9" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y9" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z9" s="45" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="46">
+        <v>46106.418194444443</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" s="56">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I10" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J10" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10" s="47" t="s">
+        <v>217</v>
+      </c>
+      <c r="L10" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M10" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N10" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O10" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q10" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="U10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="V10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X10" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z10" s="49" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="42">
+        <v>46106.418958333335</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" s="56">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H11" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J11" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L11" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="M11" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N11" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O11" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q11" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R11" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S11" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T11" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U11" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="V11" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W11" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X11" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y11" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z11" s="45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="46">
+        <v>46106.418981481482</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="56">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>226</v>
+      </c>
+      <c r="J12" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L12" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="M12" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N12" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="O12" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q12" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R12" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="S12" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T12" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U12" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="V12" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="W12" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X12" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y12" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z12" s="49" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="42">
+        <v>46106.419062499997</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>290</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="E13" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L13" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M13" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N13" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O13" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q13" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R13" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S13" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T13" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="U13" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V13" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W13" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X13" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y13" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z13" s="45" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="48" t="s">
+        <v>233</v>
+      </c>
+      <c r="E14" s="56">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>226</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="K14" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L14" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="M14" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="N14" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O14" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="P14" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q14" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R14" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S14" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="T14" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U14" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="V14" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="W14" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X14" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y14" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z14" s="49" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="42">
+        <v>46106.419988425929</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>292</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H15" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I15" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L15" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M15" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N15" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O15" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q15" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R15" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S15" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T15" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U15" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V15" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W15" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X15" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y15" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z15" s="45" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="46">
+        <v>46106.420046296298</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" s="56">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="K16" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L16" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M16" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N16" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O16" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q16" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R16" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S16" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T16" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="U16" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="V16" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="W16" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X16" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y16" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z16" s="49" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="42">
+        <v>46106.420104166667</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>294</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="E17" s="56">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="H17" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L17" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="M17" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N17" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O17" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="P17" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="S17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="T17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="W17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="X17" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y17" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z17" s="45" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="46">
+        <v>46106.420347222222</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>295</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="E18" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G18" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I18" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="K18" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L18" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M18" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N18" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O18" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P18" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q18" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R18" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S18" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T18" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U18" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="V18" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W18" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X18" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y18" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z18" s="49" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="42">
+        <v>46106.42046296296</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>296</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="E19" s="56">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H19" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I19" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L19" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M19" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N19" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O19" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P19" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q19" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R19" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="S19" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="T19" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="U19" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V19" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W19" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X19" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y19" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z19" s="45" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="K20" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L20" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M20" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N20" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O20" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P20" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q20" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R20" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S20" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T20" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U20" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="V20" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W20" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X20" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y20" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z20" s="49" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="42">
+        <v>46106.421365740738</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>256</v>
+      </c>
+      <c r="E21" s="56">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G21" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H21" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I21" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="L21" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M21" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N21" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O21" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P21" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q21" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R21" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="S21" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T21" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="U21" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="V21" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="W21" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X21" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y21" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z21" s="45" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="46">
+        <v>46106.422662037039</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>259</v>
+      </c>
+      <c r="E22" s="56">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I22" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="J22" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="K22" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="L22" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="M22" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N22" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="O22" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q22" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R22" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S22" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T22" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U22" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="V22" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="W22" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="X22" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y22" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z22" s="49" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="42">
+        <v>46106.42291666667</v>
+      </c>
+      <c r="B23" s="60" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G23" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H23" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I23" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L23" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M23" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N23" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O23" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P23" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q23" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R23" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S23" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T23" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U23" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V23" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W23" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X23" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y23" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z23" s="45" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="46">
+        <v>46106.423321759263</v>
+      </c>
+      <c r="B24" s="59" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="56">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="K24" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="L24" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M24" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N24" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O24" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q24" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="U24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="V24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X24" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z24" s="49" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="42">
+        <v>46106.443576388891</v>
+      </c>
+      <c r="B25" s="60" t="s">
+        <v>302</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="E25" s="56">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H25" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J25" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="L25" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="M25" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="N25" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="O25" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="P25" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q25" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="R25" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S25" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="T25" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="U25" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="V25" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="W25" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="X25" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y25" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z25" s="45" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="46">
+        <v>46106.445543981485</v>
+      </c>
+      <c r="B26" s="59" t="s">
+        <v>303</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>250</v>
+      </c>
+      <c r="E26" s="56">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J26" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="K26" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="L26" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="M26" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="N26" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="O26" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="P26" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q26" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R26" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="S26" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="T26" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U26" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="V26" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W26" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="X26" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y26" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z26" s="49" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="B27" s="62" t="s">
+        <v>304</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>272</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="E27" s="56">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="I27" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="K27" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="L27" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="M27" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="N27" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="O27" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="P27" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q27" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="R27" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="S27" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="T27" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="U27" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="V27" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="W27" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="X27" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y27" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z27" s="54" t="s">
+        <v>274</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Z27" xr:uid="{5B781B1C-465B-40C3-B31E-0122F766D036}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="HERNANDEZ VILLANUEVA VICTOR DANIEL"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A27:Z27">
+      <sortCondition descending="1" ref="B1:B27"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>